--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,405 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44044</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43953</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43862</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43771</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43680</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43589</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43498</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43407</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43225</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43134</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>319900</v>
+      </c>
+      <c r="E8" s="3">
         <v>294600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>281200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>290800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>341700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>312300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>317500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>313400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>356300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>332200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>328500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>253900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>274600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>300800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>147500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>239900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>274600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>268200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>253800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>234700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>269200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>268400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>257400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>243200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>287500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>488500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>253400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>234200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>202200</v>
+      </c>
+      <c r="E9" s="3">
         <v>189200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>182700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>179500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>210800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>199100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>204700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>196600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>212300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>196500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>198300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>175700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>218200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>116000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>170000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>189900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>186100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>178700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>168000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>188000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>184600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>180100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>173000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>201800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>348100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>181200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>169800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E10" s="3">
         <v>105500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>98500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>111300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>130900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>113200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>112800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>116900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>144000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>135700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>130200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>78200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>87800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>69900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>84700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>82100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>75100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>66700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>81200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>83800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>77300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>70200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>85700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>140400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>72200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>64400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1281,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1275,11 +1295,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1287,44 +1307,44 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3100</v>
-      </c>
-      <c r="O14" s="3">
-        <v>200</v>
       </c>
       <c r="P14" s="3">
         <v>200</v>
       </c>
       <c r="Q14" s="3">
+        <v>200</v>
+      </c>
+      <c r="R14" s="3">
         <v>2300</v>
-      </c>
-      <c r="R14" s="3">
-        <v>600</v>
       </c>
       <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>600</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1335,8 +1355,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1353,8 +1373,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1442,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E17" s="3">
         <v>270000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>260200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>262100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>298100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>273500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>282100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>285500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>293900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>272500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>270900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>243300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>254400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>286400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>170800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>235100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>256500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>252500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>238200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>233200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>253200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>253400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>240100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>243100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>269600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>468800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>240200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>235700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>24600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>21000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>43600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>62400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>59700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>57600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,31 +1716,32 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>400</v>
       </c>
       <c r="G20" s="3">
         <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1728,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>300</v>
       </c>
       <c r="V20" s="3">
         <v>300</v>
@@ -1749,11 +1783,11 @@
         <v>300</v>
       </c>
       <c r="X20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1772,97 +1806,103 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E21" s="3">
         <v>32200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>50200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>44700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>33000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>67200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>64300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>20200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>21600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>23000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>23900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>31600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>19100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1909,17 +1949,17 @@
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
@@ -1936,200 +1976,209 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E23" s="3">
         <v>25000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>43900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>38900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>35300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>62300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>57500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>15700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>13200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E26" s="3">
         <v>19400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>26900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>46800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>44200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>43200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>11800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>13900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>11700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E27" s="3">
         <v>19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>28900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>26900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>46800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>44200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>43200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>13800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2531,8 +2592,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2543,23 +2604,23 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>100</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,31 +2818,34 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-400</v>
       </c>
       <c r="G32" s="3">
         <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2796,19 +2866,19 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-300</v>
       </c>
       <c r="V32" s="3">
         <v>-300</v>
@@ -2817,11 +2887,11 @@
         <v>-300</v>
       </c>
       <c r="X32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2840,97 +2910,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E33" s="3">
         <v>19400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>28900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>26900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>44200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>13700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>13800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E35" s="3">
         <v>19400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>28900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>26900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>44200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>13700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>13800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44044</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43953</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43862</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43771</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43680</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43589</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43498</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43407</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43225</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43134</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,129 +3353,133 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E41" s="3">
         <v>34600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>86200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>117400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>173400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>146500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>174600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>106500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>61900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>33700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>67000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>39700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>48300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>18500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>25300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>62900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E42" s="3">
         <v>12200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>11000</v>
       </c>
       <c r="I42" s="3">
         <v>11000</v>
       </c>
       <c r="J42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K42" s="3">
         <v>15000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17400</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
@@ -3406,8 +3496,8 @@
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3445,364 +3535,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4000</v>
-      </c>
-      <c r="E43" s="3">
-        <v>3100</v>
       </c>
       <c r="F43" s="3">
         <v>3100</v>
       </c>
       <c r="G43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H43" s="3">
         <v>7800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>368300</v>
+      </c>
+      <c r="E44" s="3">
         <v>409300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>389500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>390400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>392300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>385500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>345000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>285200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>282000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>308100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>268600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>233300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>274300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>298900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>304000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>259500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>298000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>336900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>289400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>257500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>300500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>336900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>295900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>260500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>302900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>357500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>309600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>279600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E45" s="3">
         <v>25300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>10900</v>
       </c>
       <c r="T45" s="3">
         <v>10900</v>
       </c>
       <c r="U45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="V45" s="3">
         <v>9800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E46" s="3">
         <v>485400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>453600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>469700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>464400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>476900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>471200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>442000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>495700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>493100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>462600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>355300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>340200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>396000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>337600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>329600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>345000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>387700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>322700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>337300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>354300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>391300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>347600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>320600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>338200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>385800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>343500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>351800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,97 +3995,103 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>502800</v>
+      </c>
+      <c r="E48" s="3">
         <v>498800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>463200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>460000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>442200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>379300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>332300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>309500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>273500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>274300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>269600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>268000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>265100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>275600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>275300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>282800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>291300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>294400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>297000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>70600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>74500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>77300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>81600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>86300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>93000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>96000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>97300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>96200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3994,19 +4105,19 @@
         <v>44600</v>
       </c>
       <c r="G49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="H49" s="3">
         <v>44100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>43400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>44300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>44000</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
@@ -4023,8 +4134,8 @@
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -4068,8 +4179,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1023500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1043200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>976600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>989800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>966300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>914500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>861700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>812300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>786500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>784100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>750100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>642700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>623300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>689500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>629600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>628400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>647700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>693400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>628600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>418000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>438000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>477300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>437900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>415600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>442700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>492800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>451400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>458500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,97 +4709,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E57" s="3">
         <v>77400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>88300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>113800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>69100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>65600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>96500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>102400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>57700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>50900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>129600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>90000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>60700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>66100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>108400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>56500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>56300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>90900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>62600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>59400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>93800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>70600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>67800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4757,186 +4891,195 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E59" s="3">
         <v>77300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>79400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>78400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>75400</v>
       </c>
       <c r="H59" s="3">
         <v>75400</v>
       </c>
       <c r="I59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="J59" s="3">
         <v>82500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>84600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>96200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>97900</v>
       </c>
       <c r="M59" s="3">
         <v>97900</v>
       </c>
       <c r="N59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="O59" s="3">
         <v>73200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>66200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>61600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>61800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>64500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>67000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>64700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>28100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>25700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>24200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>20400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>121400</v>
+      </c>
+      <c r="E60" s="3">
         <v>154800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>135200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>157300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>163800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>189200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>199400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>153700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>161800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>194400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>130900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>125200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>195900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>151600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>122500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>130600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>175400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>121200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>70800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>84400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>116600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>86800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>56800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>81300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>114200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>92400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>86300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5013,108 +5156,114 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>26700</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>332100</v>
+      </c>
+      <c r="E62" s="3">
         <v>332900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>303700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>306900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>297000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>241600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>206700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>206000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>192100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>199800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>199500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>201700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>194900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>204700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>198500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>208500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>216300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>214400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>215900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>42800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>44900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>47000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>49600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>51500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>51800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>51700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>52300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>53300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>453600</v>
+      </c>
+      <c r="E66" s="3">
         <v>487700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>438900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>464200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>460800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>430900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>406000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>359700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>354000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>394100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>399800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>332600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>320100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>400500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>350100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>331000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>347000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>389800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>337100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>113600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>129300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>163500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>136400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>108300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>133100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>192600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>144700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>139600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>702400</v>
+      </c>
+      <c r="E72" s="3">
         <v>683900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>667200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>653500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>634300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>604200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>577800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>553500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>534900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>490100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>447900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>406700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>400500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>387100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>378400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>395800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>393500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>381000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>370500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>360400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>360300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>349500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>339100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>326700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>331900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>322500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>319900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>312600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>569900</v>
+      </c>
+      <c r="E76" s="3">
         <v>555500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>537700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>525600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>505600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>483600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>455700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>452500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>432500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>389900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>350300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>310200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>303200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>289000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>279500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>297400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>300700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>303600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>291500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>304400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>308800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>313800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>301500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>307300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>309600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>300200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>306600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>318900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44044</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43953</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43862</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43771</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43680</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43589</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43498</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43407</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43225</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43134</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E81" s="3">
         <v>19400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>28900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>26900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>44200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>13700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>13800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6806,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E83" s="3">
         <v>7100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>4300</v>
       </c>
       <c r="S83" s="3">
         <v>4300</v>
       </c>
       <c r="T83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="U83" s="3">
         <v>4100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>5300</v>
       </c>
       <c r="W83" s="3">
         <v>5300</v>
       </c>
       <c r="X83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="Y83" s="3">
         <v>5600</v>
       </c>
       <c r="Z83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AA83" s="3">
         <v>5900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E89" s="3">
         <v>20300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>27400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>76500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>63200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>69100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-42900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>19300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>36400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>23600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>31400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>42300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-2400</v>
       </c>
       <c r="W91" s="3">
         <v>-2400</v>
       </c>
       <c r="X91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-81400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,31 +7886,32 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-2500</v>
       </c>
       <c r="H96" s="3">
         <v>-2500</v>
       </c>
       <c r="I96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-2000</v>
       </c>
       <c r="K96" s="3">
         <v>-2000</v>
@@ -7686,10 +7920,10 @@
         <v>-2000</v>
       </c>
       <c r="M96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-1300</v>
       </c>
       <c r="O96" s="3">
         <v>-1300</v>
@@ -7701,7 +7935,7 @@
         <v>-1300</v>
       </c>
       <c r="R96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="S96" s="3">
         <v>-1200</v>
@@ -7710,10 +7944,10 @@
         <v>-1200</v>
       </c>
       <c r="U96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-1200</v>
       </c>
       <c r="W96" s="3">
         <v>-1200</v>
@@ -7731,10 +7965,10 @@
         <v>-1200</v>
       </c>
       <c r="AB96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AD96" s="3">
         <v>-1200</v>
@@ -7742,8 +7976,11 @@
       <c r="AE96" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8252,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-1200</v>
       </c>
       <c r="O100" s="3">
         <v>-1200</v>
       </c>
       <c r="P100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-18200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-26900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-21200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8436,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-34600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-55900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>68100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>59800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-48800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-45400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>27200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>29400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,418 +656,444 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F7" s="2">
         <v>45227</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45136</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45045</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44954</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44772</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44590</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44499</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44317</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44226</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44044</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43953</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43862</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43771</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43680</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43589</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43498</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43407</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43316</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43225</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43134</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43036</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42945</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42854</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42763</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>280200</v>
+      </c>
+      <c r="F8" s="3">
         <v>319900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>294600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>281200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>290800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>341700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>312300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>317500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>313400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>356300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>332200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>328500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>253900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>274600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>300800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>147500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>239900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>274600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>268200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>253800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>234700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>269200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>268400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>257400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>243200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>287500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>488500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>253400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>234200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>180500</v>
+      </c>
+      <c r="F9" s="3">
         <v>202200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>189200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>182700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>179500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>210800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>199100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>204700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>196600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>212300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>196500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>198300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>175700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>186800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>218200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>116000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>170000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>189900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>186100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>178700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>168000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>188000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>184600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>180100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>173000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>201800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>348100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>181200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>169800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>99700</v>
+      </c>
+      <c r="F10" s="3">
         <v>117700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>105500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>98500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>111300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>130900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>113200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>112800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>116900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>144000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>135700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>130200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>78200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>87800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>82600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>31500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>69900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>84700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>82100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>75100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>66700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>81200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>83800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>77300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>70200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>85700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>140400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>72200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>64400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1126,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,8 +1220,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,8 +1318,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1298,59 +1338,59 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>3100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>2300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1358,11 +1398,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1376,8 +1416,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1468,8 +1514,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1551,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>277900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>260200</v>
+      </c>
+      <c r="F17" s="3">
         <v>292000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>270000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>260200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>262100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>298100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>273500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>282100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>285500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>293900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>272500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>270900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>243300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>254400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>286400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>170800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>235100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>256500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>252500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>238200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>233200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>253200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>253400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>240100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>243100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>269600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>468800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>240200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>235700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F18" s="3">
         <v>27900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>24600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>21000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>28700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>43600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>38800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>35400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>27900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>62400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>59700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>57600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>20200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>14400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-23300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>4800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>18100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>15700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>15600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>16000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>15000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>17300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>19700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>13200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,8 +1783,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1726,29 +1794,29 @@
         <v>800</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="F20" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
         <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1765,35 +1833,35 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>300</v>
       </c>
       <c r="Y20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1809,100 +1877,112 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>28700</v>
+      </c>
+      <c r="F21" s="3">
         <v>36100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>32200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>28100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>35700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>50200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>44700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>40100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>33000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>67200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>64300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>61900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>14600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>24300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>18400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-19300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>9200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>22600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>19900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>20200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>7100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>21600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>20600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>23000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>6000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>23900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>31600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>19100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>4500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1952,20 +2032,20 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -1979,206 +2059,224 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F23" s="3">
         <v>28700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>25000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>21400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>29000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>43900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>38900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>35300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>27800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>62300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>59600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>57500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>10400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>20000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>14300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-23200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>18300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>15700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>15900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>16300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>15000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>17300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>17800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>19500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>13200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>5600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>4800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>11300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>8400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>15500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>15400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>14200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>4600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>4200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>3300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>4300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>7100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>7300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>5000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2367,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F26" s="3">
         <v>21900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>19400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>16500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>21600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>32700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>28900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>26900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>20600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>46800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>44200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>43200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>14700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>10100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-16200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>13700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>11800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>13900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>12000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>11700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>13000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>10700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>12100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>8200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F27" s="3">
         <v>21900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>19400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>16500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>21600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>32700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>28900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>26900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>20600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>46800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>44200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>43200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>14700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>10100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-16200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>13700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>11800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>13800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>12000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>11600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>12900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>10500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>12000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>8100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,8 +2661,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2595,11 +2717,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2607,26 +2729,26 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>100</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>-4400</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>-4400</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2637,8 +2759,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2857,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,8 +2955,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2830,29 +2970,29 @@
         <v>-800</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>-1100</v>
       </c>
       <c r="F32" s="3">
-        <v>-500</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
         <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2869,35 +3009,35 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="W32" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-300</v>
       </c>
       <c r="Y32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2913,100 +3053,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F33" s="3">
         <v>21900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>19400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>16500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>21600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>32700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>28900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>26900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>20600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>46800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>44200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>43200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>14700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>10100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-16200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>13700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>11800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>13800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>12000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>11700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>12900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>10500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>12000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>8100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3249,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F35" s="3">
         <v>21900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>19400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>16500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>21600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>32700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>28900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>26900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>20600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>46800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>44200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>43200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>14700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>10100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-16200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>13700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>11800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>13800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>12000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>11700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>12900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>10500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>12000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>8100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F38" s="2">
         <v>45227</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45136</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45045</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44954</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44772</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44590</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44499</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44317</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44226</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44044</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43953</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43862</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43771</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43680</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43589</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43498</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43407</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43316</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43225</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43134</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43036</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42945</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42854</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42763</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3490,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,138 +3526,146 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F41" s="3">
         <v>59900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>34600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>32600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>51400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>37200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>51600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>86200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>117400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>173400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>146500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>174600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>106500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>46700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>76900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>13100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>61900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>33700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>37500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>21600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>67000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>39700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>38400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>35300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>48300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>21100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>18500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>25300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>62900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>11200</v>
+        <v>12600</v>
       </c>
       <c r="E42" s="3">
         <v>12200</v>
       </c>
       <c r="F42" s="3">
+        <v>11200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>12200</v>
+      </c>
+      <c r="H42" s="3">
         <v>11500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>11600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>10400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>11000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>15000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>17800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>17400</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
@@ -3499,11 +3679,11 @@
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3538,376 +3718,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3100</v>
+        <v>5900</v>
       </c>
       <c r="E43" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
       <c r="F43" s="3">
         <v>3100</v>
       </c>
       <c r="G43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>10700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>14200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>10000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>7900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>8400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>6800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>6300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>3900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>6300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>7400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>4400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>411600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>346400</v>
+      </c>
+      <c r="F44" s="3">
         <v>368300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>409300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>389500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>390400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>392300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>385500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>345000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>285200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>282000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>308100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>268600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>233300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>274300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>298900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>304000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>259500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>298000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>336900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>289400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>257500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>300500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>336900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>295900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>260500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>302900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>357500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>309600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>279600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F45" s="3">
         <v>19500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>25300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>16800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>13300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>16900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>18100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>14600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>10300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>12400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>11900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>8400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>10700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>13400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>14200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>10900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>9800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>11500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>11800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>12100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>13200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>5600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>6900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>7000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>6700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>4700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>481300</v>
+      </c>
+      <c r="F46" s="3">
         <v>462000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>485400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>453600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>469700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>464400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>476900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>471200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>442000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>495700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>493100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>462600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>355300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>340200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>396000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>337600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>329600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>345000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>387700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>322700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>337300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>354300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>391300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>347600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>320600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>338200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>385800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>343500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>351800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3998,105 +4208,117 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>518100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>502500</v>
+      </c>
+      <c r="F48" s="3">
         <v>502800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>498800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>463200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>460000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>442200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>379300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>332300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>309500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>273500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>274300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>269600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>268000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>265100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>275600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>275300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>282800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>291300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>294400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>297000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>70600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>74500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>77300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>81600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>86300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>93000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>96000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>97300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>96200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>44600</v>
+        <v>56200</v>
       </c>
       <c r="E49" s="3">
         <v>44600</v>
@@ -4108,22 +4330,22 @@
         <v>44600</v>
       </c>
       <c r="H49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="I49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="J49" s="3">
         <v>44100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>43400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>44300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>44000</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
@@ -4137,11 +4359,11 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -4182,8 +4404,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4502,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,100 +4600,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F52" s="3">
         <v>14000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>14400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>15200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>15400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>15600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>14900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>13900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>16800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>17400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>16600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>17800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>19500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>18100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>17900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>16700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>15900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>11400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>11300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>8900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>10100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>9300</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>8700</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>8600</v>
       </c>
       <c r="AA52" s="3">
         <v>8700</v>
       </c>
       <c r="AB52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AD52" s="3">
         <v>11400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>10900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>10600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>10500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4796,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1092600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1042000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1023500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1043200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>976600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>989800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>966300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>914500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>861700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>812300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>786500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>784100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>750100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>642700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>623300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>689500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>629600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>628400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>647700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>693400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>628600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>418000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>438000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>477300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>437900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>415600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>442700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>492800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>451400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>458500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4934,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,100 +4970,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>58300</v>
+      </c>
+      <c r="F57" s="3">
         <v>42900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>77400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>55900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>78900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>88300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>113800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>116800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>69100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>65600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>96500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>102400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>57700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>50900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>129600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>90000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>60700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>66100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>108400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>56500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>48700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>56300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>90900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>62600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>41700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>59400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>93800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>70600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>67800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4894,192 +5162,210 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>69600</v>
+      </c>
+      <c r="F59" s="3">
         <v>78500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>77300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>79400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>78400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>75400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>75400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>82500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>84600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>96200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>97900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>97900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>73200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>74300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>66200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>61600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>61800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>64500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>67000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>64700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>22100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>28100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>25700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>24200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>15000</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>21900</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>20400</v>
       </c>
       <c r="AD59" s="3">
         <v>21900</v>
       </c>
       <c r="AE59" s="3">
+        <v>20400</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>21900</v>
+      </c>
+      <c r="AG59" s="3">
         <v>18500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>127900</v>
+      </c>
+      <c r="F60" s="3">
         <v>121400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>154800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>135200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>157300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>163800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>189200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>199400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>153700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>161800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>194400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>200300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>130900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>125200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>195900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>151600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>122500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>130600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>175400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>121200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>70800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>84400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>116600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>86800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>56800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>81300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>114200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>92400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>86300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5159,111 +5445,123 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>26700</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>345600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>330800</v>
+      </c>
+      <c r="F62" s="3">
         <v>332100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>332900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>303700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>306900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>297000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>241600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>206700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>206000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>192100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>199800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>199500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>201700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>194900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>204700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>198500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>208500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>216300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>214400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>215900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>42800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>44900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>47000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>49600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>51500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>51800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>51700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>52300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>53300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5652,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5750,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5848,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>494800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>458600</v>
+      </c>
+      <c r="F66" s="3">
         <v>453600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>487700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>438900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>464200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>460800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>430900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>406000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>359700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>354000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>394100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>399800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>332600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>320100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>400500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>350100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>331000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>347000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>389800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>337100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>113600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>129300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>163500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>136400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>108300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>133100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>192600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>144700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>139600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5986,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +6080,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6178,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6276,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6374,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>728200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>714600</v>
+      </c>
+      <c r="F72" s="3">
         <v>702400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>683900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>667200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>653500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>634300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>604200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>577800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>553500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>534900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>490100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>447900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>406700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>400500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>387100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>378400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>395800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>393500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>381000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>370500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>360400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>360300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>349500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>339100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>326700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>331900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>322500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>319900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>312600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6570,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6668,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6766,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>597800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>583400</v>
+      </c>
+      <c r="F76" s="3">
         <v>569900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>555500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>537700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>525600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>505600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>483600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>455700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>452500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>432500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>389900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>350300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>310200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>303200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>289000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>279500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>297400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>300700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>303600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>291500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>304400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>308800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>313800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>301500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>307300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>309600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>300200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>306600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>318900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6962,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F80" s="2">
         <v>45227</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45136</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45045</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44954</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44772</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44590</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44499</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44317</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44226</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44044</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43953</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43862</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43771</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43680</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43589</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43498</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43407</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43316</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43225</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43134</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43036</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42945</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42854</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42763</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F81" s="3">
         <v>21900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>19400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>16500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>21600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>32700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>28900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>26900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>20600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>46800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>44200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>43200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>14700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>10100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-16200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>13700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>11800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>13800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>12000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>11700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>12900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>10500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>12000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>8100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,8 +7203,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6816,91 +7214,97 @@
         <v>7400</v>
       </c>
       <c r="E83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>6700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>6600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>6200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>5700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>5100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>4800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>4000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>3800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>4300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>4100</v>
       </c>
       <c r="V83" s="3">
         <v>4300</v>
       </c>
       <c r="W83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>5300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>5300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>5600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>5600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>5900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>6000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>12000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>5800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>6000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7395,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7493,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7591,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7689,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7787,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>53400</v>
+      </c>
+      <c r="F89" s="3">
         <v>47000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>20300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>31500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>10000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-8800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>17700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>27400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>40600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>76500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>63200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>69100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-42900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>38900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>18000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>19300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-9300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>36400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>23600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>5700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>8500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>31400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>35500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>42300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7925,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-13000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-15600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-13600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-13500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-23300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-26900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-8100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-9200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +8117,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +8215,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-13000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-15600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-14800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-12100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-23300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-23900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-81400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-25500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-4100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-4000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-9200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,49 +8353,51 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G96" s="3">
         <v>-2700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-2900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-2400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-2500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-2500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-2000</v>
       </c>
       <c r="M96" s="3">
         <v>-2000</v>
       </c>
       <c r="N96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-1300</v>
       </c>
       <c r="Q96" s="3">
         <v>-1300</v>
@@ -7938,22 +8406,22 @@
         <v>-1300</v>
       </c>
       <c r="S96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="T96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="U96" s="3">
         <v>-1200</v>
       </c>
       <c r="V96" s="3">
-        <v>-2000</v>
+        <v>-1200</v>
       </c>
       <c r="W96" s="3">
         <v>-1200</v>
       </c>
       <c r="X96" s="3">
-        <v>-1200</v>
+        <v>-2000</v>
       </c>
       <c r="Y96" s="3">
         <v>-1200</v>
@@ -7968,19 +8436,25 @@
         <v>-1200</v>
       </c>
       <c r="AC96" s="3">
-        <v>-2400</v>
+        <v>-1200</v>
       </c>
       <c r="AD96" s="3">
         <v>-1200</v>
       </c>
       <c r="AE96" s="3">
-        <v>-1200</v>
+        <v>-2400</v>
       </c>
       <c r="AF96" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8545,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8643,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,100 +8741,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-8700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-12400</v>
       </c>
       <c r="I100" s="3">
         <v>-2500</v>
       </c>
       <c r="J100" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="L100" s="3">
         <v>-25100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-5500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-5900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-3000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-18200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-26900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-8200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-21200</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>-20400</v>
       </c>
       <c r="AA100" s="3">
         <v>-1200</v>
       </c>
       <c r="AB100" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8439,96 +8937,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F102" s="3">
         <v>25300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-18800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>14200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-14500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-34600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-31300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-55900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>26900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-28100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>68100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>59800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>63800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-48800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>28200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>15800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-45400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>27300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>27200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>2500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>29400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,444 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E7" s="2">
         <v>45416</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43862</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43771</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43680</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43589</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43498</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43407</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43316</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43225</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43134</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>332700</v>
+      </c>
+      <c r="E8" s="3">
         <v>300400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>280200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>319900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>294600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>281200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>290800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>341700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>312300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>317500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>313400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>356300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>332200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>328500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>253900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>274600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>300800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>147500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>239900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>274600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>268200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>253800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>234700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>269200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>268400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>257400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>243200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>287500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>488500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>253400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>234200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>212800</v>
+      </c>
+      <c r="E9" s="3">
         <v>193600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>180500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>202200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>189200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>182700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>179500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>210800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>199100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>204700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>196600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>212300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>196500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>198300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>175700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>186800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>218200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>116000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>170000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>189900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>186100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>178700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>168000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>188000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>184600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>180100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>173000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>201800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>348100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>181200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>169800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E10" s="3">
         <v>106800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>99700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>117700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>105500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>98500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>130900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>113200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>112800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>116900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>144000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>135700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>130200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>78200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>87800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>82600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>69900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>84700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>82100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>75100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>66700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>81200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>83800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>77300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>70200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>85700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>140400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>72200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>64400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1128,8 +1141,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,8 +1240,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,8 +1341,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1344,11 +1364,11 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1356,44 +1376,44 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3100</v>
-      </c>
-      <c r="R14" s="3">
-        <v>200</v>
       </c>
       <c r="S14" s="3">
         <v>200</v>
       </c>
       <c r="T14" s="3">
+        <v>200</v>
+      </c>
+      <c r="U14" s="3">
         <v>2300</v>
-      </c>
-      <c r="U14" s="3">
-        <v>600</v>
       </c>
       <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>600</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1404,8 +1424,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1422,8 +1442,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1520,8 +1543,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1553,204 +1579,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>302600</v>
+      </c>
+      <c r="E17" s="3">
         <v>277900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>260200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>292000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>270000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>260200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>262100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>298100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>273500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>282100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>285500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>293900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>272500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>270900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>243300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>254400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>286400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>170800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>235100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>256500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>252500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>238200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>233200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>253200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>253400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>240100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>243100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>269600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>468800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>240200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>235700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E18" s="3">
         <v>22500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>21000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>62400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>59700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>57600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>18100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>17300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>17900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1785,40 +1818,41 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
       </c>
       <c r="J20" s="3">
         <v>400</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1839,19 +1873,19 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>300</v>
       </c>
       <c r="Y20" s="3">
         <v>300</v>
@@ -1860,11 +1894,11 @@
         <v>300</v>
       </c>
       <c r="AA20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1883,106 +1917,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E21" s="3">
         <v>30700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>32200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>28100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>50200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>33000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>67200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>64300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>18400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-19300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>21600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>23900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>31600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>19100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2038,17 +2078,17 @@
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
@@ -2065,218 +2105,227 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E23" s="3">
         <v>23200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>43900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>35300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>62300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>57500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>16300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>19500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>13200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-7000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2373,204 +2422,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E26" s="3">
         <v>17300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>46800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>43200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>13700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>13900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>11700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>13000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E27" s="3">
         <v>17300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>46800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>43200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>13700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>13800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>11600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>8100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2667,8 +2725,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2723,8 +2784,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2735,23 +2796,23 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2765,8 +2826,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2863,8 +2927,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2961,40 +3028,43 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
       </c>
       <c r="J32" s="3">
         <v>-400</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3015,19 +3085,19 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-300</v>
       </c>
       <c r="Y32" s="3">
         <v>-300</v>
@@ -3036,11 +3106,11 @@
         <v>-300</v>
       </c>
       <c r="AA32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3059,106 +3129,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E33" s="3">
         <v>17300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>46800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>43200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>13700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>13800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>11700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>8100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3255,209 +3331,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E35" s="3">
         <v>17300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>46800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>43200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>13700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>13800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>11700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>8100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E38" s="2">
         <v>45416</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43862</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43771</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43680</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43589</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43498</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43407</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43316</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43225</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43134</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3492,8 +3577,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3528,147 +3614,151 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E41" s="3">
         <v>56900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>51400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>51600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>117400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>173400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>146500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>174600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>106500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>61900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>33700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>67000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>39700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>35300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>48300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>21100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>18500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>25300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>62900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E42" s="3">
         <v>12600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10400</v>
-      </c>
-      <c r="K42" s="3">
-        <v>11000</v>
       </c>
       <c r="L42" s="3">
         <v>11000</v>
       </c>
       <c r="M42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="N42" s="3">
         <v>15000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17400</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>8</v>
@@ -3685,8 +3775,8 @@
       <c r="U42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3724,400 +3814,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E43" s="3">
         <v>5900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>3100</v>
       </c>
       <c r="I43" s="3">
         <v>3100</v>
       </c>
       <c r="J43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>425500</v>
+      </c>
+      <c r="E44" s="3">
         <v>411600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>346400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>368300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>409300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>389500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>390400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>392300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>385500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>345000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>285200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>282000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>308100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>268600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>233300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>274300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>298900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>304000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>259500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>298000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>336900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>289400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>257500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>300500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>336900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>295900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>260500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>302900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>357500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>309600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>279600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E45" s="3">
         <v>18000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>16800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5500</v>
-      </c>
-      <c r="V45" s="3">
-        <v>10900</v>
       </c>
       <c r="W45" s="3">
         <v>10900</v>
       </c>
       <c r="X45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Y45" s="3">
         <v>9800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>13200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>537100</v>
+      </c>
+      <c r="E46" s="3">
         <v>505000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>481300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>462000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>485400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>453600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>469700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>464400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>476900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>471200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>442000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>495700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>493100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>462600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>355300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>340200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>396000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>337600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>329600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>345000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>387700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>322700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>337300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>354300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>391300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>347600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>320600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>338200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>385800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>343500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>351800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4214,114 +4319,120 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>508600</v>
+      </c>
+      <c r="E48" s="3">
         <v>518100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>502500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>502800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>498800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>463200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>460000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>442200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>379300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>332300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>309500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>273500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>274300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>269600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>268000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>265100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>275600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>275300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>282800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>291300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>294400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>297000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>70600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>74500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>77300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>81600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>86300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>93000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>96000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>97300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>96200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E49" s="3">
         <v>56200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>44600</v>
       </c>
       <c r="F49" s="3">
         <v>44600</v>
@@ -4336,19 +4447,19 @@
         <v>44600</v>
       </c>
       <c r="J49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="K49" s="3">
         <v>44100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>43400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44000</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
@@ -4365,8 +4476,8 @@
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -4410,8 +4521,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4508,8 +4622,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4606,106 +4723,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E52" s="3">
         <v>13300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4802,106 +4925,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1115000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1092600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1042000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1023500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1043200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>976600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>989800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>966300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>914500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>861700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>812300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>786500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>784100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>750100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>642700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>623300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>689500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>629600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>628400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>647700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>693400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>628600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>418000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>438000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>477300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>437900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>415600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>442700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>492800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>451400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>458500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4936,8 +5065,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4972,106 +5102,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E57" s="3">
         <v>71200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>42900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>77400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>88300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>113800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>116800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>69100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>65600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>96500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>102400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>57700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>50900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>129600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>90000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>60700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>66100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>108400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>56500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>56300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>90900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>62600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>41700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>59400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>93800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>70600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>67800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5168,204 +5302,213 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E59" s="3">
         <v>78000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>69600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>78500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>79400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>75400</v>
       </c>
       <c r="K59" s="3">
         <v>75400</v>
       </c>
       <c r="L59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="M59" s="3">
         <v>82500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>84600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>96200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>97900</v>
       </c>
       <c r="P59" s="3">
         <v>97900</v>
       </c>
       <c r="Q59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="R59" s="3">
         <v>73200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>66200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>61600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>61800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>64500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>67000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>64700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>28100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>25700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>24200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>21900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>20400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>21900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E60" s="3">
         <v>149200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>127900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>121400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>154800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>135200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>157300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>163800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>189200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>199400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>153700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>161800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>194400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>130900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>125200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>195900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>151600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>122500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>130600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>175400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>121200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>70800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>84400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>116600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>86800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>56800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>81300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>114200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>92400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>86300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5451,117 +5594,123 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>26700</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>336500</v>
+      </c>
+      <c r="E62" s="3">
         <v>345600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>330800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>332100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>332900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>303700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>306900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>297000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>241600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>206700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>206000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>192100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>199800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>199500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>201700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>194900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>204700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>198500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>208500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>216300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>214400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>215900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>44900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>47000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>49600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>51500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>51800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>51700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>52300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>53300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5658,8 +5807,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5756,8 +5908,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5854,106 +6009,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>496500</v>
+      </c>
+      <c r="E66" s="3">
         <v>494800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>458600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>453600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>487700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>438900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>464200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>460800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>430900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>406000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>359700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>354000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>394100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>399800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>332600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>320100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>400500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>350100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>331000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>347000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>389800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>337100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>113600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>129300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>163500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>136400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>108300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>133100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>192600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>144700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>139600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5988,8 +6149,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6086,8 +6248,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6184,8 +6349,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6282,8 +6450,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6380,106 +6551,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E72" s="3">
         <v>728200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>714600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>702400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>683900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>667200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>653500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>634300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>604200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>577800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>553500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>534900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>490100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>447900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>406700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>400500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>387100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>378400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>395800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>393500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>381000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>370500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>360400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>360300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>349500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>339100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>326700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>331900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>322500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>319900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>312600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6576,8 +6753,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6674,8 +6854,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6772,106 +6955,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>618500</v>
+      </c>
+      <c r="E76" s="3">
         <v>597800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>583400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>569900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>555500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>537700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>525600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>505600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>483600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>455700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>452500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>432500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>389900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>350300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>310200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>303200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>289000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>279500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>297400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>300700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>303600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>291500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>304400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>308800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>313800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>301500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>307300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>309600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>300200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>306600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>318900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6968,209 +7157,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E80" s="2">
         <v>45416</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43862</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43771</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43680</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43589</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43498</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43407</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43316</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43225</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43134</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E81" s="3">
         <v>17300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>46800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>43200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>13700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>13800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>11700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>8100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7205,106 +7403,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3800</v>
-      </c>
-      <c r="U83" s="3">
-        <v>4300</v>
       </c>
       <c r="V83" s="3">
         <v>4300</v>
       </c>
       <c r="W83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="X83" s="3">
         <v>4100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4300</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>5300</v>
       </c>
       <c r="Z83" s="3">
         <v>5300</v>
       </c>
       <c r="AA83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="AB83" s="3">
         <v>5600</v>
       </c>
       <c r="AC83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AD83" s="3">
         <v>5900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7401,8 +7603,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7499,8 +7704,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7597,8 +7805,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7695,8 +7906,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7793,106 +8007,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E89" s="3">
         <v>17100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>53400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>47000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>76500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>63200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-26000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>69100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-42900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>18000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>19300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>36400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>23600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>31400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>42300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7927,106 +8147,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-2400</v>
       </c>
       <c r="Z91" s="3">
         <v>-2400</v>
       </c>
       <c r="AA91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8123,8 +8347,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8221,106 +8448,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-54800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-81400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8355,8 +8588,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8364,31 +8598,31 @@
         <v>-3700</v>
       </c>
       <c r="E96" s="3">
-        <v>-3300</v>
+        <v>-3700</v>
       </c>
       <c r="F96" s="3">
         <v>-3300</v>
       </c>
       <c r="G96" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H96" s="3">
         <v>-2700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-2500</v>
       </c>
       <c r="K96" s="3">
         <v>-2500</v>
       </c>
       <c r="L96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-2000</v>
       </c>
       <c r="N96" s="3">
         <v>-2000</v>
@@ -8397,10 +8631,10 @@
         <v>-2000</v>
       </c>
       <c r="P96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-1300</v>
       </c>
       <c r="R96" s="3">
         <v>-1300</v>
@@ -8412,7 +8646,7 @@
         <v>-1300</v>
       </c>
       <c r="U96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="V96" s="3">
         <v>-1200</v>
@@ -8421,10 +8655,10 @@
         <v>-1200</v>
       </c>
       <c r="X96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-1200</v>
       </c>
       <c r="Z96" s="3">
         <v>-1200</v>
@@ -8442,10 +8676,10 @@
         <v>-1200</v>
       </c>
       <c r="AE96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AG96" s="3">
         <v>-1200</v>
@@ -8453,8 +8687,11 @@
       <c r="AH96" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8551,8 +8788,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8649,8 +8889,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8747,106 +8990,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-1200</v>
       </c>
       <c r="R100" s="3">
         <v>-1200</v>
       </c>
       <c r="S100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T100" s="3">
         <v>-1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-18200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-26900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-21200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8943,102 +9192,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-42100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-34600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-31300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-55900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>68100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>59800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-30100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>63800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-48800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>28200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-45400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>27300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>27200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>29400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,457 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E7" s="2">
         <v>45507</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45416</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45325</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43862</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43771</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43680</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43589</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43498</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43407</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43316</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43225</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43134</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>306900</v>
+      </c>
+      <c r="E8" s="3">
         <v>332700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>280200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>319900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>294600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>281200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>290800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>341700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>312300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>317500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>313400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>356300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>332200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>328500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>253900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>274600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>300800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>147500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>239900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>274600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>268200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>253800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>234700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>269200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>268400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>257400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>243200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>287500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>488500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>253400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>234200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E9" s="3">
         <v>212800</v>
       </c>
-      <c r="E9" s="3">
-        <v>193600</v>
-      </c>
       <c r="F9" s="3">
+        <v>193400</v>
+      </c>
+      <c r="G9" s="3">
         <v>180500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>202200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>189200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>182700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>179500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>210800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>199100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>204700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>196600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>212300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>196500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>198300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>175700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>186800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>218200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>116000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>170000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>189900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>186100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>178700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>168000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>188000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>184600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>180100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>173000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>201800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>348100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>181200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>169800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E10" s="3">
         <v>119900</v>
       </c>
-      <c r="E10" s="3">
-        <v>106800</v>
-      </c>
       <c r="F10" s="3">
+        <v>107000</v>
+      </c>
+      <c r="G10" s="3">
         <v>99700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>117700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>105500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>98500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>111300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>130900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>113200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>112800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>116900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>144000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>135700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>130200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>78200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>87800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>82600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>31500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>69900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>84700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>82100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>75100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>66700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>81200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>83800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>77300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>70200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>85700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>140400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>72200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>64400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1243,8 +1256,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,8 +1360,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1355,11 +1374,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3">
+        <v>500</v>
+      </c>
+      <c r="G14" s="3">
+        <v>800</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1367,11 +1386,11 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1379,44 +1398,44 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3100</v>
-      </c>
-      <c r="S14" s="3">
-        <v>200</v>
       </c>
       <c r="T14" s="3">
         <v>200</v>
       </c>
       <c r="U14" s="3">
+        <v>200</v>
+      </c>
+      <c r="V14" s="3">
         <v>2300</v>
-      </c>
-      <c r="V14" s="3">
-        <v>600</v>
       </c>
       <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1427,8 +1446,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1445,31 +1464,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1546,8 +1568,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,210 +1605,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>282400</v>
+      </c>
+      <c r="E17" s="3">
         <v>302600</v>
       </c>
-      <c r="E17" s="3">
-        <v>277900</v>
-      </c>
       <c r="F17" s="3">
+        <v>277400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>259400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>292000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J17" s="3">
         <v>260200</v>
       </c>
-      <c r="G17" s="3">
-        <v>292000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>270000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>260200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>262100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>298100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>273500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>282100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>285500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>293900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>272500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>270900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>243300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>254400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>286400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>170800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>235100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>256500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>252500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>238200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>233200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>253200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>253400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>240100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>243100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>269600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>468800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>240200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>235700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E18" s="3">
         <v>30100</v>
       </c>
-      <c r="E18" s="3">
-        <v>22500</v>
-      </c>
       <c r="F18" s="3">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="G18" s="3">
+        <v>20800</v>
+      </c>
+      <c r="H18" s="3">
         <v>27900</v>
       </c>
-      <c r="H18" s="3">
-        <v>24600</v>
-      </c>
       <c r="I18" s="3">
-        <v>21000</v>
+        <v>24700</v>
       </c>
       <c r="J18" s="3">
+        <v>20900</v>
+      </c>
+      <c r="K18" s="3">
         <v>28700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>38800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>62400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>59700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>57600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>17300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>19700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1819,43 +1851,44 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>400</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>400</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1876,19 +1909,19 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>300</v>
       </c>
       <c r="Z20" s="3">
         <v>300</v>
@@ -1897,11 +1930,11 @@
         <v>300</v>
       </c>
       <c r="AB20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1920,109 +1953,115 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>38500</v>
+        <v>32200</v>
       </c>
       <c r="E21" s="3">
-        <v>30700</v>
+        <v>37800</v>
       </c>
       <c r="F21" s="3">
-        <v>28700</v>
+        <v>30400</v>
       </c>
       <c r="G21" s="3">
-        <v>36100</v>
+        <v>28400</v>
       </c>
       <c r="H21" s="3">
-        <v>32200</v>
+        <v>35300</v>
       </c>
       <c r="I21" s="3">
-        <v>28100</v>
+        <v>31800</v>
       </c>
       <c r="J21" s="3">
+        <v>27600</v>
+      </c>
+      <c r="K21" s="3">
         <v>35700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>50200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>44700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>33000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>67200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>64300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-19300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>19900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>20200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>21600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>23000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>23900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>31600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>19100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2081,17 +2120,17 @@
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
@@ -2108,224 +2147,233 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E23" s="3">
         <v>30600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>28700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>43900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>35300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>62300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>57500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>16300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>15000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>17300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>19500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>13200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2425,210 +2473,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>26900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>44200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>43200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>14700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>13700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>11800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>13000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>12100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E27" s="3">
         <v>22600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>26900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>46800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>44200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>43200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>13700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>13800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2728,8 +2785,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2787,8 +2847,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2799,24 +2859,24 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2829,8 +2889,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2930,8 +2993,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3031,43 +3097,46 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-400</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>-400</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -3088,19 +3157,19 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-300</v>
       </c>
       <c r="Z32" s="3">
         <v>-300</v>
@@ -3109,11 +3178,11 @@
         <v>-300</v>
       </c>
       <c r="AB32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3132,109 +3201,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E33" s="3">
         <v>22600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>26900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>46800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>44200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>43200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>13700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>13800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3334,215 +3409,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E35" s="3">
         <v>22600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>26900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>46800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>44200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>43200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>13700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>13800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E38" s="2">
         <v>45507</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45416</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45325</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43862</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43771</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43680</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43589</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43498</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43407</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43316</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43225</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43134</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3578,8 +3662,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3615,154 +3700,158 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E41" s="3">
         <v>71600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>51400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>117400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>173400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>146500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>174600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>106500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>61900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>33700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>67000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>39700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>35300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>21100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>18500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>25300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>62900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E42" s="3">
         <v>12800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10400</v>
-      </c>
-      <c r="L42" s="3">
-        <v>11000</v>
       </c>
       <c r="M42" s="3">
         <v>11000</v>
       </c>
       <c r="N42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O42" s="3">
         <v>15000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3778,8 +3867,8 @@
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3817,435 +3906,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>3100</v>
       </c>
       <c r="J43" s="3">
         <v>3100</v>
       </c>
       <c r="K43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>406600</v>
+      </c>
+      <c r="E44" s="3">
         <v>425500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>411600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>346400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>368300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>409300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>389500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>390400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>392300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>385500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>345000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>285200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>282000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>308100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>268600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>233300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>274300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>298900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>304000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>259500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>298000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>336900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>289400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>257500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>300500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>336900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>295900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>260500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>302900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>357500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>309600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>279600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E45" s="3">
         <v>21700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>10900</v>
       </c>
       <c r="X45" s="3">
         <v>10900</v>
       </c>
       <c r="Y45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Z45" s="3">
         <v>9800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E46" s="3">
         <v>537100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>505000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>481300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>462000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>485400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>453600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>469700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>464400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>476900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>471200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>442000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>495700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>493100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>462600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>355300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>340200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>396000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>337600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>329600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>345000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>387700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>322700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>337300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>354300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>391300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>347600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>320600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>338200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>385800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>343500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>351800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4322,123 +4426,129 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>525200</v>
+      </c>
+      <c r="E48" s="3">
         <v>508600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>518100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>502500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>502800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>498800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>463200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>460000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>442200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>379300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>332300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>309500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>273500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>274300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>269600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>268000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>265100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>275600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>275300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>282800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>291300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>294400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>297000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>70600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>74500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>77300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>81600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>86300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>93000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>96000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>97300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>96200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E49" s="3">
         <v>56400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>56200</v>
       </c>
-      <c r="F49" s="3">
-        <v>44600</v>
-      </c>
       <c r="G49" s="3">
-        <v>44600</v>
+        <v>57100</v>
       </c>
       <c r="H49" s="3">
         <v>44600</v>
@@ -4450,20 +4560,20 @@
         <v>44600</v>
       </c>
       <c r="K49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="L49" s="3">
         <v>44100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>43400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>44000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4479,8 +4589,8 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4524,8 +4634,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4625,8 +4738,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4726,109 +4842,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E52" s="3">
         <v>12900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13300</v>
       </c>
-      <c r="F52" s="3">
-        <v>13600</v>
-      </c>
       <c r="G52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H52" s="3">
         <v>14000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>19500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4928,109 +5050,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1124400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1115000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1092600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1042000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1023500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1043200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>976600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>989800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>966300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>914500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>861700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>812300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>786500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>784100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>750100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>642700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>623300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>689500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>629600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>628400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>647700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>693400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>628600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>418000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>438000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>477300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>437900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>415600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>442700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>492800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>451400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>458500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5066,8 +5194,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5103,132 +5232,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E57" s="3">
         <v>73900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>42900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>77400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>55900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>78900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>88300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>113800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>69100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>65600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>96500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>102400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>57700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>129600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>90000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>60700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>66100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>108400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>56500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>48700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>56300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>90900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>62600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>41700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>59400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>93800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>70600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>67800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>58400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>55900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>57100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>57300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>58100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5305,233 +5438,242 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>86100</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>78000</v>
+        <v>5500</v>
       </c>
       <c r="F59" s="3">
-        <v>69600</v>
+        <v>4800</v>
       </c>
       <c r="G59" s="3">
-        <v>78500</v>
+        <v>6200</v>
       </c>
       <c r="H59" s="3">
-        <v>77300</v>
+        <v>4100</v>
       </c>
       <c r="I59" s="3">
-        <v>79400</v>
+        <v>4300</v>
       </c>
       <c r="J59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K59" s="3">
         <v>78400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>75400</v>
       </c>
       <c r="L59" s="3">
         <v>75400</v>
       </c>
       <c r="M59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="N59" s="3">
         <v>82500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>84600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>96200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>97900</v>
       </c>
       <c r="Q59" s="3">
         <v>97900</v>
       </c>
       <c r="R59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="S59" s="3">
         <v>73200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>66200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>61600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>61800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>64500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>67000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>64700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>28100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>25700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>24200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>21900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>20400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>21900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E60" s="3">
         <v>160000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>149200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>127900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>121400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>154800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>135200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>157300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>163800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>189200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>199400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>153700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>161800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>194400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>200300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>130900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>125200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>195900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>151600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>122500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>130600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>175400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>121200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>70800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>84400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>116600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>86800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>56800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>81300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>114200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>92400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>86300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>304600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>313300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>301400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>305300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>307300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>279200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5597,120 +5739,126 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>26700</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>336500</v>
+        <v>17700</v>
       </c>
       <c r="E62" s="3">
-        <v>345600</v>
+        <v>16800</v>
       </c>
       <c r="F62" s="3">
-        <v>330800</v>
+        <v>16300</v>
       </c>
       <c r="G62" s="3">
-        <v>332100</v>
+        <v>12100</v>
       </c>
       <c r="H62" s="3">
-        <v>332900</v>
+        <v>10200</v>
       </c>
       <c r="I62" s="3">
-        <v>303700</v>
+        <v>11000</v>
       </c>
       <c r="J62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K62" s="3">
         <v>306900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>297000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>241600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>206700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>206000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>192100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>199800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>199500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>201700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>194900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>204700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>198500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>208500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>216300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>214400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>215900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>44900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>47000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>49600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>51500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>51800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>51700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>52300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>53300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5810,8 +5958,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5911,8 +6062,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6012,109 +6166,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>488800</v>
+      </c>
+      <c r="E66" s="3">
         <v>496500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>494800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>458600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>453600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>487700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>438900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>464200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>460800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>430900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>406000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>359700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>354000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>394100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>399800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>332600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>320100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>400500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>350100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>331000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>347000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>389800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>337100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>113600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>129300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>163500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>136400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>108300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>133100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>192600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>144700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>139600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6150,8 +6310,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6251,8 +6412,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6352,8 +6516,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6453,8 +6620,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6554,109 +6724,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>747000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>728200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>714600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>702400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>683900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>667200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>653500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>634300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>604200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>577800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>553500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>534900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>490100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>447900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>406700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>400500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>387100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>378400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>395800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>393500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>381000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>370500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>360400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>360300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>349500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>339100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>326700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>331900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>322500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>319900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>312600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6756,8 +6932,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6857,8 +7036,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6958,109 +7140,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>635700</v>
+      </c>
+      <c r="E76" s="3">
         <v>618500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>597800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>583400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>569900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>555500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>537700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>525600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>505600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>483600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>455700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>452500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>432500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>389900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>350300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>310200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>303200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>289000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>279500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>297400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>300700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>303600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>291500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>304400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>308800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>313800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>301500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>307300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>309600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>300200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>306600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>318900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7160,215 +7348,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E80" s="2">
         <v>45507</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45416</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45325</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43862</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43771</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43680</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43589</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43498</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43407</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43316</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43225</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43134</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E81" s="3">
         <v>22600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>26900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>46800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>44200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>43200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>13700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>13800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7404,109 +7601,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7700</v>
+        <v>7400</v>
       </c>
       <c r="E83" s="3">
-        <v>7400</v>
+        <v>7100</v>
       </c>
       <c r="F83" s="3">
-        <v>7600</v>
+        <v>6700</v>
       </c>
       <c r="G83" s="3">
-        <v>7400</v>
+        <v>6600</v>
       </c>
       <c r="H83" s="3">
-        <v>7100</v>
+        <v>6200</v>
       </c>
       <c r="I83" s="3">
-        <v>6700</v>
+        <v>5700</v>
       </c>
       <c r="J83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3800</v>
-      </c>
-      <c r="V83" s="3">
-        <v>4300</v>
       </c>
       <c r="W83" s="3">
         <v>4300</v>
       </c>
       <c r="X83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>4100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4300</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>5300</v>
       </c>
       <c r="AA83" s="3">
         <v>5300</v>
       </c>
       <c r="AB83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="AC83" s="3">
         <v>5600</v>
       </c>
       <c r="AD83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AE83" s="3">
         <v>5900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7606,8 +7807,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7707,8 +7911,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7808,8 +8015,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7909,8 +8119,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8010,109 +8223,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E89" s="3">
         <v>23700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>47000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>76500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>63200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-26000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>69100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-42900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>18000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>19300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>36400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>23600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>31400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>42300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8148,109 +8367,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-2400</v>
       </c>
       <c r="AA91" s="3">
         <v>-2400</v>
       </c>
       <c r="AB91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8350,8 +8573,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8451,109 +8677,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-54800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-81400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8589,43 +8821,44 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3700</v>
+        <v>3700</v>
       </c>
       <c r="E96" s="3">
-        <v>-3700</v>
+        <v>3700</v>
       </c>
       <c r="F96" s="3">
-        <v>-3300</v>
+        <v>3700</v>
       </c>
       <c r="G96" s="3">
-        <v>-3300</v>
+        <v>3300</v>
       </c>
       <c r="H96" s="3">
-        <v>-2700</v>
+        <v>3300</v>
       </c>
       <c r="I96" s="3">
-        <v>-2900</v>
+        <v>2700</v>
       </c>
       <c r="J96" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-2500</v>
       </c>
       <c r="L96" s="3">
         <v>-2500</v>
       </c>
       <c r="M96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-2000</v>
       </c>
       <c r="O96" s="3">
         <v>-2000</v>
@@ -8634,10 +8867,10 @@
         <v>-2000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-1300</v>
       </c>
       <c r="S96" s="3">
         <v>-1300</v>
@@ -8649,7 +8882,7 @@
         <v>-1300</v>
       </c>
       <c r="V96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="W96" s="3">
         <v>-1200</v>
@@ -8658,10 +8891,10 @@
         <v>-1200</v>
       </c>
       <c r="Y96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AA96" s="3">
         <v>-1200</v>
@@ -8679,10 +8912,10 @@
         <v>-1200</v>
       </c>
       <c r="AF96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AH96" s="3">
         <v>-1200</v>
@@ -8690,8 +8923,11 @@
       <c r="AI96" s="3">
         <v>-1200</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8791,8 +9027,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8892,8 +9131,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8993,8 +9235,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9002,123 +9247,126 @@
         <v>-3600</v>
       </c>
       <c r="E100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-1200</v>
       </c>
       <c r="S100" s="3">
         <v>-1200</v>
       </c>
       <c r="T100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U100" s="3">
         <v>-1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-18200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9195,105 +9443,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E102" s="3">
         <v>14700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-42100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-34600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-55900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>26900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>68100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>59800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-30100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>63800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-48800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>28200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>15800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-45400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>27300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>27200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>29400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,469 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45598</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45507</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45416</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45325</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43862</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43771</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43680</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43589</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43498</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43407</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43316</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43225</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43134</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E8" s="3">
         <v>306900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>332700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>280200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>319900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>294600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>281200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>290800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>341700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>312300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>317500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>313400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>356300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>332200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>328500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>253900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>274600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>147500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>239900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>274600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>268200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>253800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>234700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>269200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>268400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>257400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>243200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>287500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>488500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>253400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>234200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>196300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>212800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>193400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>180500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>202200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>189200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>182700</v>
+      </c>
+      <c r="L9" s="3">
+        <v>179500</v>
+      </c>
+      <c r="M9" s="3">
+        <v>210800</v>
+      </c>
+      <c r="N9" s="3">
+        <v>199100</v>
+      </c>
+      <c r="O9" s="3">
+        <v>204700</v>
+      </c>
+      <c r="P9" s="3">
+        <v>196600</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>212300</v>
+      </c>
+      <c r="R9" s="3">
         <v>196500</v>
       </c>
-      <c r="E9" s="3">
-        <v>212800</v>
-      </c>
-      <c r="F9" s="3">
-        <v>193400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>180500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>202200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>189200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>182700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>179500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>210800</v>
-      </c>
-      <c r="M9" s="3">
-        <v>199100</v>
-      </c>
-      <c r="N9" s="3">
-        <v>204700</v>
-      </c>
-      <c r="O9" s="3">
-        <v>196600</v>
-      </c>
-      <c r="P9" s="3">
-        <v>212300</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>196500</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>198300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>175700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>186800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>218200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>116000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>170000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>189900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>186100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>178700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>168000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>188000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>184600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>180100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>173000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>201800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>348100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>181200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>169800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>110400</v>
+        <v>91700</v>
       </c>
       <c r="E10" s="3">
+        <v>110600</v>
+      </c>
+      <c r="F10" s="3">
         <v>119900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>107000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>99700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>117700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>105500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>98500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>111300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>130900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>113200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>112800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>116900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>144000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>135700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>130200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>78200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>87800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>82600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>31500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>69900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>84700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>82100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>75100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>66700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>81200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>83800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>77300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>70200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>85700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>140400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>72200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>64400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1168,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1259,8 +1273,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,37 +1380,40 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>400</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1401,44 +1421,44 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>200</v>
       </c>
       <c r="U14" s="3">
         <v>200</v>
       </c>
       <c r="V14" s="3">
+        <v>200</v>
+      </c>
+      <c r="W14" s="3">
         <v>2300</v>
-      </c>
-      <c r="W14" s="3">
-        <v>600</v>
       </c>
       <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1449,8 +1469,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1467,35 +1487,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E15" s="3">
         <v>7600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1571,8 +1594,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,216 +1632,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>282400</v>
+        <v>248900</v>
       </c>
       <c r="E17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="F17" s="3">
         <v>302600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>277400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>259400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>292000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>270000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>260200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>262100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>298100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>273500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>282100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>285500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>293900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>272500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>270900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>243300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>254400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>286400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>170800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>235100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>256500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>252500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>238200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>233200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>253200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>253400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>240100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>243100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>269600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>468800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>240200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>235700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>24500</v>
+        <v>14100</v>
       </c>
       <c r="E18" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F18" s="3">
         <v>30100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>35400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>62400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>59700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>57600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-23300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>18100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>17300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>19700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>13200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1852,13 +1885,14 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1878,20 +1912,20 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>400</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>400</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1912,19 +1946,19 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>300</v>
       </c>
       <c r="AA20" s="3">
         <v>300</v>
@@ -1933,11 +1967,11 @@
         <v>300</v>
       </c>
       <c r="AC20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1956,117 +1990,123 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>32200</v>
+        <v>22500</v>
       </c>
       <c r="E21" s="3">
+        <v>32500</v>
+      </c>
+      <c r="F21" s="3">
         <v>37800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>28400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>35300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>31800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>50200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>44700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>40100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>67200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>64300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>61900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>24300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-19300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>19900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>20200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>21600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>20600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>23000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>23900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>31600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>19100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>100</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -2123,17 +2163,17 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
@@ -2150,230 +2190,239 @@
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>200</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E23" s="3">
         <v>25500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>43900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>38900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>35300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>62300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>57500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-23200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>18300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>15900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>19500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>13200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2476,216 +2525,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E26" s="3">
         <v>19200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>46800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>44200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>43200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>14700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-16200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>13700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>13900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>11700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>13000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E27" s="3">
         <v>19200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>46800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>44200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>43200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>13700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>13800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>8100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2788,8 +2846,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2850,8 +2911,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2862,24 +2923,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>100</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2892,8 +2953,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2996,8 +3060,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,13 +3167,16 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -3126,20 +3196,20 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>-400</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>-400</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3160,19 +3230,19 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-300</v>
       </c>
       <c r="AA32" s="3">
         <v>-300</v>
@@ -3181,11 +3251,11 @@
         <v>-300</v>
       </c>
       <c r="AC32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3204,112 +3274,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E33" s="3">
         <v>19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>46800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>44200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>43200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>13700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>13800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>8100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3412,221 +3488,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E35" s="3">
         <v>19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>46800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>44200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>43200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>13700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>13800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>8100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45598</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45507</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45416</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45325</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43862</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43771</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43680</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43589</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43498</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43407</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43316</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43225</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43134</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,8 +3748,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,160 +3787,164 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E41" s="3">
         <v>77200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>56900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>51400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>51600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>117400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>173400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>146500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>174600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>106500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>76900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>61900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>33700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>67000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>39700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>38400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>35300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>48300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>21100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>18500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>25300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>62900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E42" s="3">
         <v>13900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10400</v>
-      </c>
-      <c r="M42" s="3">
-        <v>11000</v>
       </c>
       <c r="N42" s="3">
         <v>11000</v>
       </c>
       <c r="O42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="P42" s="3">
         <v>15000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3870,8 +3960,8 @@
       <c r="W42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3909,424 +3999,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>3100</v>
       </c>
       <c r="K43" s="3">
         <v>3100</v>
       </c>
       <c r="L43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>385600</v>
+      </c>
+      <c r="E44" s="3">
         <v>406600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>425500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>411600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>346400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>368300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>409300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>389500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>390400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>392300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>385500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>345000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>285200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>282000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>308100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>268600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>233300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>274300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>298900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>304000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>259500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>298000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>336900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>289400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>257500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>300500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>336900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>295900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>260500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>302900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>357500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>309600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>279600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E45" s="3">
         <v>20700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5500</v>
-      </c>
-      <c r="X45" s="3">
-        <v>10900</v>
       </c>
       <c r="Y45" s="3">
         <v>10900</v>
       </c>
       <c r="Z45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AA45" s="3">
         <v>9800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>13200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>536100</v>
+      </c>
+      <c r="E46" s="3">
         <v>527000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>537100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>505000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>481300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>462000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>485400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>453600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>469700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>464400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>476900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>471200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>442000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>495700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>493100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>462600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>355300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>340200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>396000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>337600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>329600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>345000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>387700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>322700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>337300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>354300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>391300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>347600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>320600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>338200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>385800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>343500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>351800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4351,8 +4456,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4429,112 +4534,118 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>516400</v>
+      </c>
+      <c r="E48" s="3">
         <v>525200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>508600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>518100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>502500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>502800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>498800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>463200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>460000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>442200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>379300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>332300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>309500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>273500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>274300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>269600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>268000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>265100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>275600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>275300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>282800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>291300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>294400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>297000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>70600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>74500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>77300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>81600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>86300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>93000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>96000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>97300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>96200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4542,16 +4653,16 @@
         <v>59000</v>
       </c>
       <c r="E49" s="3">
+        <v>59000</v>
+      </c>
+      <c r="F49" s="3">
         <v>56400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>56200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>57100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>44600</v>
       </c>
       <c r="I49" s="3">
         <v>44600</v>
@@ -4563,20 +4674,20 @@
         <v>44600</v>
       </c>
       <c r="L49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="M49" s="3">
         <v>44100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>43400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>44300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>44000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4592,8 +4703,8 @@
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4637,8 +4748,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4741,8 +4855,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4845,112 +4962,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E52" s="3">
         <v>13200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5053,112 +5176,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1124100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1124400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1115000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1092600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1042000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1023500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1043200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>976600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>989800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>966300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>914500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>861700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>812300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>786500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>784100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>750100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>642700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>623300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>689500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>629600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>628400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>647700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>693400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>628600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>418000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>438000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>477300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>437900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>415600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>442700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>492800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>451400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>458500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5195,8 +5324,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5233,139 +5363,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E57" s="3">
         <v>57300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>73900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>58300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>42900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>77400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>55900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>88300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>113800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>116800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>69100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>65600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>96500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>102400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>57700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>129600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>90000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>60700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>66100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>108400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>56500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>48700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>56300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>90900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>62600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>41700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>59400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>93800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>70600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>67800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E58" s="3">
         <v>58400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>55900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>56000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>57100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>57300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>58100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5441,8 +5575,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5450,234 +5587,240 @@
         <v>8</v>
       </c>
       <c r="E59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F59" s="3">
         <v>5500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4300</v>
       </c>
       <c r="J59" s="3">
         <v>4300</v>
       </c>
       <c r="K59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L59" s="3">
         <v>78400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>75400</v>
       </c>
       <c r="M59" s="3">
         <v>75400</v>
       </c>
       <c r="N59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="O59" s="3">
         <v>82500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>96200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>97900</v>
       </c>
       <c r="R59" s="3">
         <v>97900</v>
       </c>
       <c r="S59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="T59" s="3">
         <v>73200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>66200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>61600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>61800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>64500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>67000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>64700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>28100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>25700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>24200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>21900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>20400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>21900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E60" s="3">
         <v>135800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>160000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>149200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>127900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>121400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>154800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>135200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>157300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>163800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>189200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>199400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>153700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>161800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>194400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>130900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>125200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>195900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>151600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>122500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>130600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>175400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>121200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>70800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>84400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>116600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>86800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>56800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>81300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>114200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>92400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>86300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E61" s="3">
         <v>317700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>304600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>313300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>301400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>305300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>307300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>279200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5742,123 +5885,129 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>26700</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E62" s="3">
         <v>17700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>306900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>297000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>241600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>206700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>206000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>192100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>199800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>199500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>201700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>194900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>204700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>198500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>208500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>216300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>214400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>215900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>42800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>44900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>47000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>49600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>51500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>51800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>51700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>52300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>53300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6110,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6065,8 +6217,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6169,112 +6324,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>475100</v>
+      </c>
+      <c r="E66" s="3">
         <v>488800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>496500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>494800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>458600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>453600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>487700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>438900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>464200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>460800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>430900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>406000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>359700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>354000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>394100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>399800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>332600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>320100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>400500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>350100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>331000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>347000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>389800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>337100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>113600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>129300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>163500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>136400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>108300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>133100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>192600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>144700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>139600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6311,8 +6472,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6415,8 +6577,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6519,8 +6684,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6623,8 +6791,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6727,8 +6898,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6736,103 +6910,106 @@
         <v>8</v>
       </c>
       <c r="E72" s="3">
+        <v>762500</v>
+      </c>
+      <c r="F72" s="3">
         <v>747000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>728200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>714600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>702400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>683900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>667200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>653500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>634300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>604200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>577800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>553500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>534900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>490100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>447900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>406700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>400500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>387100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>378400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>395800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>393500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>381000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>370500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>360400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>360300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>349500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>339100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>326700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>331900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>322500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>319900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>312600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6935,8 +7112,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7039,8 +7219,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7143,112 +7326,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>649000</v>
+      </c>
+      <c r="E76" s="3">
         <v>635700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>618500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>597800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>583400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>569900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>555500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>537700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>525600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>505600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>483600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>455700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>452500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>432500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>389900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>350300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>310200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>303200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>289000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>279500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>297400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>300700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>303600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>291500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>304400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>308800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>313800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>301500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>307300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>309600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>300200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>306600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>318900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7351,221 +7540,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45598</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45507</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45416</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45325</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43862</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43771</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43680</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43589</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43498</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43407</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43316</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43225</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43134</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E81" s="3">
         <v>19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>46800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>44200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>43200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>13700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>13800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>8100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7602,112 +7800,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3800</v>
-      </c>
-      <c r="W83" s="3">
-        <v>4300</v>
       </c>
       <c r="X83" s="3">
         <v>4300</v>
       </c>
       <c r="Y83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>4100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4300</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>5300</v>
       </c>
       <c r="AB83" s="3">
         <v>5300</v>
       </c>
       <c r="AC83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="AD83" s="3">
         <v>5600</v>
       </c>
       <c r="AE83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AF83" s="3">
         <v>5900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7810,8 +8012,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7914,8 +8119,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8018,8 +8226,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8122,8 +8333,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8226,112 +8440,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E89" s="3">
         <v>17300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>53400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>47000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>20300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>76500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>63200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-26000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>69100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-42900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>19300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>36400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>23600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>31400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>42300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8368,112 +8588,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-2400</v>
       </c>
       <c r="AB91" s="3">
         <v>-2400</v>
       </c>
       <c r="AC91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8576,8 +8800,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8680,112 +8907,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-54800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-81400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8822,8 +9055,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8837,31 +9071,31 @@
         <v>3700</v>
       </c>
       <c r="G96" s="3">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="H96" s="3">
         <v>3300</v>
       </c>
       <c r="I96" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J96" s="3">
         <v>2700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-2500</v>
       </c>
       <c r="M96" s="3">
         <v>-2500</v>
       </c>
       <c r="N96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-2000</v>
       </c>
       <c r="P96" s="3">
         <v>-2000</v>
@@ -8870,10 +9104,10 @@
         <v>-2000</v>
       </c>
       <c r="R96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-1300</v>
       </c>
       <c r="T96" s="3">
         <v>-1300</v>
@@ -8885,7 +9119,7 @@
         <v>-1300</v>
       </c>
       <c r="W96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="X96" s="3">
         <v>-1200</v>
@@ -8894,10 +9128,10 @@
         <v>-1200</v>
       </c>
       <c r="Z96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AB96" s="3">
         <v>-1200</v>
@@ -8915,10 +9149,10 @@
         <v>-1200</v>
       </c>
       <c r="AG96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AI96" s="3">
         <v>-1200</v>
@@ -8926,8 +9160,11 @@
       <c r="AJ96" s="3">
         <v>-1200</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9030,8 +9267,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9134,8 +9374,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9238,112 +9481,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="E100" s="3">
         <v>-3600</v>
       </c>
       <c r="F100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-1200</v>
       </c>
       <c r="T100" s="3">
         <v>-1200</v>
       </c>
       <c r="U100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-26900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-21200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-20400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9617,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9446,108 +9695,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E102" s="3">
         <v>5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-42100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-34600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-55900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-28100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>68100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>59800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-30100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>63800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-48800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>28200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-45400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>27300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>27200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>29400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E14" s="3">
         <v>400</v>
@@ -1400,8 +1400,8 @@
       <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
-        <v>800</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1639,7 +1639,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>248900</v>
+        <v>249400</v>
       </c>
       <c r="E17" s="3">
         <v>282000</v>
@@ -1651,7 +1651,7 @@
         <v>277400</v>
       </c>
       <c r="H17" s="3">
-        <v>259400</v>
+        <v>260200</v>
       </c>
       <c r="I17" s="3">
         <v>292000</v>
@@ -1746,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>14100</v>
+        <v>13500</v>
       </c>
       <c r="E18" s="3">
         <v>24900</v>
@@ -1758,7 +1758,7 @@
         <v>23000</v>
       </c>
       <c r="H18" s="3">
-        <v>20800</v>
+        <v>20000</v>
       </c>
       <c r="I18" s="3">
         <v>27900</v>
@@ -1891,8 +1891,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-100</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1999,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>22500</v>
+        <v>21800</v>
       </c>
       <c r="E21" s="3">
         <v>32500</v>
@@ -2011,7 +2011,7 @@
         <v>30400</v>
       </c>
       <c r="H21" s="3">
-        <v>28400</v>
+        <v>27600</v>
       </c>
       <c r="I21" s="3">
         <v>35300</v>
@@ -2105,8 +2105,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>-100</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -3175,8 +3175,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>100</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -4662,7 +4662,7 @@
         <v>56200</v>
       </c>
       <c r="H49" s="3">
-        <v>57100</v>
+        <v>44600</v>
       </c>
       <c r="I49" s="3">
         <v>44600</v>
@@ -4971,7 +4971,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="E52" s="3">
         <v>13200</v>
@@ -4983,7 +4983,7 @@
         <v>13300</v>
       </c>
       <c r="H52" s="3">
-        <v>1100</v>
+        <v>13600</v>
       </c>
       <c r="I52" s="3">
         <v>14000</v>
@@ -5583,8 +5583,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>5900</v>
       </c>
       <c r="E59" s="3">
         <v>4600</v>
@@ -6906,8 +6906,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>773400</v>
       </c>
       <c r="E72" s="3">
         <v>762500</v>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,482 +656,495 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45598</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45507</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45416</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45325</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44590</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44044</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43953</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43862</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43771</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43680</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43589</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43498</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43407</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43316</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43225</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43134</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43036</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>277700</v>
+      </c>
+      <c r="E8" s="3">
         <v>262900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>306900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>332700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>280200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>319900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>294600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>281200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>290800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>341700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>312300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>317500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>313400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>356300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>332200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>328500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>253900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>274600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>300800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>147500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>239900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>274600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>268200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>253800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>234700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>269200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>268400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>257400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>243200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>287500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>488500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>253400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>234200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>181900</v>
+      </c>
+      <c r="E9" s="3">
         <v>171300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>196300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>212800</v>
       </c>
-      <c r="G9" s="3">
-        <v>193400</v>
-      </c>
       <c r="H9" s="3">
+        <v>193600</v>
+      </c>
+      <c r="I9" s="3">
         <v>180500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>202200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>189200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>182700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>179500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>210800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>199100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>204700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>196600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>212300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>196500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>198300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>175700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>186800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>218200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>116000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>170000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>189900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>186100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>178700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>168000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>188000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>184600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>180100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>173000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>201800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>348100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>181200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>169800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E10" s="3">
         <v>91700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>119900</v>
       </c>
-      <c r="G10" s="3">
-        <v>107000</v>
-      </c>
       <c r="H10" s="3">
+        <v>106800</v>
+      </c>
+      <c r="I10" s="3">
         <v>99700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>117700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>105500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>98500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>111300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>130900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>113200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>112800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>116900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>144000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>135700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>130200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>78200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>87800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>82600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>31500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>69900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>84700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>82100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>75100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>66700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>81200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>83800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>77300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>70200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>85700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>140400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>72200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>64400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,8 +1182,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1276,8 +1290,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1383,25 +1400,28 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1412,11 +1432,11 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1424,44 +1444,44 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3100</v>
-      </c>
-      <c r="U14" s="3">
-        <v>200</v>
       </c>
       <c r="V14" s="3">
         <v>200</v>
       </c>
       <c r="W14" s="3">
+        <v>200</v>
+      </c>
+      <c r="X14" s="3">
         <v>2300</v>
-      </c>
-      <c r="X14" s="3">
-        <v>600</v>
       </c>
       <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1472,8 +1492,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1490,8 +1510,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1499,29 +1522,29 @@
         <v>8300</v>
       </c>
       <c r="E15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F15" s="3">
         <v>7600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7400</v>
       </c>
-      <c r="H15" s="3">
-        <v>7600</v>
-      </c>
       <c r="I15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J15" s="3">
         <v>7400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1597,8 +1620,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1659,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>265800</v>
+      </c>
+      <c r="E17" s="3">
         <v>249400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>282000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>302600</v>
       </c>
-      <c r="G17" s="3">
-        <v>277400</v>
-      </c>
       <c r="H17" s="3">
+        <v>277500</v>
+      </c>
+      <c r="I17" s="3">
         <v>260200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>292000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>270000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>262100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>298100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>273500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>282100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>285500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>293900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>272500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>270900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>243300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>254400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>286400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>170800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>235100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>256500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>252500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>238200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>233200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>253200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>253400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>240100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>243100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>269600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>468800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>240200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>235700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30100</v>
       </c>
-      <c r="G18" s="3">
-        <v>23000</v>
-      </c>
       <c r="H18" s="3">
+        <v>22800</v>
+      </c>
+      <c r="I18" s="3">
         <v>20000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>27900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>35400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>62400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>59700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>57600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-23300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>18100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>16000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>19700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,8 +1919,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1915,20 +1949,20 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>400</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1949,19 +1983,19 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>300</v>
       </c>
       <c r="AB20" s="3">
         <v>300</v>
@@ -1970,11 +2004,11 @@
         <v>300</v>
       </c>
       <c r="AD20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1993,123 +2027,129 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21800</v>
+        <v>20300</v>
       </c>
       <c r="E21" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F21" s="3">
         <v>32500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37800</v>
       </c>
-      <c r="G21" s="3">
-        <v>30400</v>
-      </c>
       <c r="H21" s="3">
+        <v>30200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>24600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>35300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>31800</v>
+      </c>
+      <c r="L21" s="3">
         <v>27600</v>
       </c>
-      <c r="I21" s="3">
-        <v>35300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>31800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>27600</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>50200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>44700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>40100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>33000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>67200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>64300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>61900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>24300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>18400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>19900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>21600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>20600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>23000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>23900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>31600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>-100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -2166,17 +2206,17 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
@@ -2193,236 +2233,245 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>200</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E23" s="3">
         <v>18200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>28700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>35300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>27800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>62300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>59600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>57500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-23200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>15700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>16300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>15000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>19500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2528,222 +2577,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E26" s="3">
         <v>14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>46800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>44200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>43200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-16200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>13900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>13000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E27" s="3">
         <v>14700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>32700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>20600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>46800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>43200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>13700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2849,8 +2907,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2914,8 +2975,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2926,24 +2987,24 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>100</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2956,8 +3017,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3127,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,8 +3237,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3199,20 +3269,20 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>-400</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3233,19 +3303,19 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-300</v>
       </c>
       <c r="AB32" s="3">
         <v>-300</v>
@@ -3254,11 +3324,11 @@
         <v>-300</v>
       </c>
       <c r="AD32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3277,115 +3347,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E33" s="3">
         <v>14700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>32700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>20600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>46800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>43200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>13700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>13800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3567,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E35" s="3">
         <v>14700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>32700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>20600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>46800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>43200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>13700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>13800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45598</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45507</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45416</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45325</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44590</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44044</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43953</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43862</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43771</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43680</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43589</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43498</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43407</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43316</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43225</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43134</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43036</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +3834,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,166 +3874,170 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E41" s="3">
         <v>108700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>117400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>173400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>146500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>174600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>106500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>46700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>76900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>61900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>33700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>67000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>39700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>35300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>48300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>18500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>62900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E42" s="3">
         <v>14400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10400</v>
-      </c>
-      <c r="N42" s="3">
-        <v>11000</v>
       </c>
       <c r="O42" s="3">
         <v>11000</v>
       </c>
       <c r="P42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="Q42" s="3">
         <v>15000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>17400</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3963,8 +4053,8 @@
       <c r="X42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -4002,436 +4092,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E43" s="3">
         <v>9000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>3100</v>
       </c>
       <c r="L43" s="3">
         <v>3100</v>
       </c>
       <c r="M43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N43" s="3">
         <v>7800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>428400</v>
+      </c>
+      <c r="E44" s="3">
         <v>385600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>406600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>425500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>411600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>346400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>368300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>409300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>389500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>390400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>392300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>385500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>345000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>285200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>282000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>308100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>268600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>233300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>274300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>298900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>304000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>259500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>298000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>336900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>289400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>257500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>300500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>336900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>295900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>260500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>302900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>357500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>309600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>279600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E45" s="3">
         <v>18400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5500</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>10900</v>
       </c>
       <c r="Z45" s="3">
         <v>10900</v>
       </c>
       <c r="AA45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AB45" s="3">
         <v>9800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>13200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>548600</v>
+      </c>
+      <c r="E46" s="3">
         <v>536100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>527000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>537100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>505000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>481300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>462000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>485400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>453600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>469700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>464400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>476900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>471200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>442000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>495700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>493100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>462600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>355300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>340200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>396000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>337600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>329600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>345000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>387700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>322700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>337300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>354300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>391300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>347600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>320600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>338200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>385800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>343500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>351800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4459,8 +4564,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4537,115 +4642,121 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>520200</v>
+      </c>
+      <c r="E48" s="3">
         <v>516400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>525200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>508600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>518100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>502500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>502800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>498800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>463200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>460000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>442200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>379300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>332300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>309500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>273500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>274300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>269600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>268000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>265100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>275600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>275300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>282800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>291300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>294400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>297000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>70600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>74500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>77300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>81600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>86300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>93000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>96000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>97300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>96200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4653,19 +4764,19 @@
         <v>59000</v>
       </c>
       <c r="E49" s="3">
+        <v>70200</v>
+      </c>
+      <c r="F49" s="3">
         <v>59000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>56400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>56200</v>
       </c>
-      <c r="H49" s="3">
-        <v>44600</v>
-      </c>
       <c r="I49" s="3">
-        <v>44600</v>
+        <v>57100</v>
       </c>
       <c r="J49" s="3">
         <v>44600</v>
@@ -4677,20 +4788,20 @@
         <v>44600</v>
       </c>
       <c r="M49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="N49" s="3">
         <v>44100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>43400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>44300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>44000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4706,8 +4817,8 @@
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4751,8 +4862,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +4972,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,115 +5082,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12600</v>
+        <v>12300</v>
       </c>
       <c r="E52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F52" s="3">
         <v>13200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13300</v>
       </c>
-      <c r="H52" s="3">
-        <v>13600</v>
-      </c>
       <c r="I52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J52" s="3">
         <v>14000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>19500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,115 +5302,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1140200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1124100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1124400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1115000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1092600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1042000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1023500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1043200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>976600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>989800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>966300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>914500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>861700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>812300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>786500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>784100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>750100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>642700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>623300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>689500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>629600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>628400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>647700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>693400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>628600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>418000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>438000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>477300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>437900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>415600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>442700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>492800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>451400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>458500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5454,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,145 +5494,149 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E57" s="3">
         <v>52000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>73900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>58300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>42900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>77400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>55900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>78900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>88300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>113800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>116800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>69100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>65600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>96500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>102400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>57700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>50900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>129600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>90000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>60700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>66100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>108400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>56500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>48700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>56300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>90900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>62600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>41700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>59400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>93800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>70600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>67800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E58" s="3">
         <v>53000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>58400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>55900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>56000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>57100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>57300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>58100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5578,252 +5712,261 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>4300</v>
       </c>
       <c r="K59" s="3">
         <v>4300</v>
       </c>
       <c r="L59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M59" s="3">
         <v>78400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>75400</v>
       </c>
       <c r="N59" s="3">
         <v>75400</v>
       </c>
       <c r="O59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="P59" s="3">
         <v>82500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>96200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>97900</v>
       </c>
       <c r="S59" s="3">
         <v>97900</v>
       </c>
       <c r="T59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="U59" s="3">
         <v>73200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>66200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>61600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>61800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>64500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>67000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>64700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>22100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>28100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>25700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>24200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>21900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>20400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E60" s="3">
         <v>130400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>135800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>160000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>149200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>127900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>121400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>135200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>157300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>163800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>189200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>199400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>153700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>161800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>194400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>200300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>130900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>125200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>195900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>151600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>122500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>130600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>175400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>121200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>70800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>84400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>116600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>86800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>56800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>81300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>114200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>92400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>86300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E61" s="3">
         <v>315000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>317700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>304600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>313300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>301400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>305300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>307300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>279200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5888,126 +6031,132 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>26700</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E62" s="3">
         <v>10900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>306900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>297000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>241600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>206700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>206000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>192100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>199800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>199500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>201700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>194900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>204700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>198500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>208500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>216300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>214400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>215900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>42800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>44900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>47000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>49600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>51500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>51800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>51700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>52300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>53300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6262,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6220,8 +6372,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,115 +6482,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>486600</v>
+      </c>
+      <c r="E66" s="3">
         <v>475100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>488800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>496500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>494800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>458600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>453600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>487700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>438900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>464200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>460800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>430900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>406000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>359700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>354000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>394100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>399800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>332600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>320100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>400500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>350100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>331000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>347000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>389800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>337100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>113600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>129300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>163500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>136400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>108300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>133100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>192600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>144700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>139600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +6634,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +6742,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +6852,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +6962,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,115 +7072,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>778500</v>
+      </c>
+      <c r="E72" s="3">
         <v>773400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>762500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>747000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>728200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>714600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>702400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>683900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>667200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>653500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>634300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>604200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>577800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>553500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>534900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>490100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>447900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>406700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>400500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>387100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>378400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>395800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>393500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>381000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>370500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>360400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>360300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>349500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>339100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>326700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>331900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>322500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>319900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>312600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7292,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7402,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,115 +7512,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>653600</v>
+      </c>
+      <c r="E76" s="3">
         <v>649000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>635700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>618500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>597800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>583400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>569900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>555500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>537700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>525600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>505600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>483600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>455700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>452500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>432500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>389900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>350300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>310200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>303200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>289000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>279500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>297400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>300700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>303600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>291500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>304400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>308800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>313800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>301500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>307300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>309600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>300200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>306600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>318900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +7732,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45598</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45507</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45416</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45325</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44590</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44044</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43953</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43862</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43771</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43680</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43589</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43498</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43407</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43316</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43225</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43134</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43036</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E81" s="3">
         <v>14700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>32700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>20600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>46800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>43200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>13700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>13800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,115 +7999,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7600</v>
+        <v>7400</v>
       </c>
       <c r="E83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3800</v>
-      </c>
-      <c r="X83" s="3">
-        <v>4300</v>
       </c>
       <c r="Y83" s="3">
         <v>4300</v>
       </c>
       <c r="Z83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>4100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4300</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>5300</v>
       </c>
       <c r="AC83" s="3">
         <v>5300</v>
       </c>
       <c r="AD83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="AE83" s="3">
         <v>5600</v>
       </c>
       <c r="AF83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AG83" s="3">
         <v>5900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>12000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>6000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8217,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8327,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +8437,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +8547,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +8657,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E89" s="3">
         <v>44600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>47000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>40600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>76500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>63200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-26000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>69100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-42900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>38900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>18000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>19300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>36400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>23600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>31400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>35500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>42300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +8809,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-2400</v>
       </c>
       <c r="AC91" s="3">
         <v>-2400</v>
       </c>
       <c r="AD91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9027,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9137,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-81400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-25500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,13 +9289,14 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>3700</v>
+        <v>4400</v>
       </c>
       <c r="E96" s="3">
         <v>3700</v>
@@ -9074,31 +9308,31 @@
         <v>3700</v>
       </c>
       <c r="H96" s="3">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="I96" s="3">
         <v>3300</v>
       </c>
       <c r="J96" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K96" s="3">
         <v>2700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-2500</v>
       </c>
       <c r="N96" s="3">
         <v>-2500</v>
       </c>
       <c r="O96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q96" s="3">
         <v>-2000</v>
@@ -9107,10 +9341,10 @@
         <v>-2000</v>
       </c>
       <c r="S96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-1300</v>
       </c>
       <c r="U96" s="3">
         <v>-1300</v>
@@ -9122,7 +9356,7 @@
         <v>-1300</v>
       </c>
       <c r="X96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="Y96" s="3">
         <v>-1200</v>
@@ -9131,10 +9365,10 @@
         <v>-1200</v>
       </c>
       <c r="AA96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AC96" s="3">
         <v>-1200</v>
@@ -9152,10 +9386,10 @@
         <v>-1200</v>
       </c>
       <c r="AH96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AJ96" s="3">
         <v>-1200</v>
@@ -9163,8 +9397,11 @@
       <c r="AK96" s="3">
         <v>-1200</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +9507,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +9617,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,115 +9727,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-3600</v>
       </c>
       <c r="F100" s="3">
         <v>-3600</v>
       </c>
       <c r="G100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H100" s="3">
         <v>-4400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-1200</v>
       </c>
       <c r="U100" s="3">
         <v>-1200</v>
       </c>
       <c r="V100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-26900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-21200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-20400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9620,8 +9869,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9698,111 +9947,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E102" s="3">
         <v>31400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-42100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>39100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-34600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-55900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-28100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>68100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>59800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-30100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>63800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-48800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>28200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>15800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-45400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>27300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>27200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>29400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,508 +656,520 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45962</v>
+      </c>
+      <c r="E7" s="2">
         <v>45871</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45780</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45689</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45598</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45507</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45416</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45325</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45227</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45136</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45045</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44954</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44863</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44772</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44590</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44499</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44317</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44226</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44044</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43953</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43862</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43771</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43680</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43589</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43498</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43407</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43316</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43225</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43134</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43036</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42945</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42854</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42763</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>297200</v>
+      </c>
+      <c r="E8" s="3">
         <v>306400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>277700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>262900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>306900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>332700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>280200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>319900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>294600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>281200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>290800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>341700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>312300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>317500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>313400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>356300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>332200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>328500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>253900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>274600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>300800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>147500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>239900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>274600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>268200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>253800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>234700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>269200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>268400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>257400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>243200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>287500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>488500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>253400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>234200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E9" s="3">
         <v>187600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>181900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>171300</v>
       </c>
-      <c r="G9" s="3">
-        <v>196300</v>
-      </c>
       <c r="H9" s="3">
+        <v>196500</v>
+      </c>
+      <c r="I9" s="3">
         <v>212800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>193600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>180500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>202200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>189200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>182700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>179500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>210800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>199100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>204700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>196600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>212300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>196500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>198300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>175700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>186800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>218200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>116000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>170000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>189900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>186100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>178700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>168000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>188000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>184600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>180100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>173000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>201800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>348100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>181200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>169800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>111800</v>
+      </c>
+      <c r="E10" s="3">
         <v>118800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>95800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>91700</v>
       </c>
-      <c r="G10" s="3">
-        <v>110600</v>
-      </c>
       <c r="H10" s="3">
+        <v>110400</v>
+      </c>
+      <c r="I10" s="3">
         <v>119900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>106800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>99700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>117700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>105500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>98500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>111300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>130900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>113200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>112800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>116900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>144000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>135700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>130200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>78200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>87800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>82600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>31500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>69900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>84700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>82100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>75100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>66700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>81200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>83800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>77300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>70200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>85700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>140400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>72200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>64400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1197,8 +1209,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1310,8 +1323,11 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1423,8 +1439,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1434,21 +1453,21 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>400</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1458,11 +1477,11 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1470,44 +1489,44 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3100</v>
-      </c>
-      <c r="W14" s="3">
-        <v>200</v>
       </c>
       <c r="X14" s="3">
         <v>200</v>
       </c>
       <c r="Y14" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2300</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>600</v>
       </c>
       <c r="AA14" s="3">
         <v>600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1518,8 +1537,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1536,44 +1555,47 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E15" s="3">
         <v>8400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6700</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1649,8 +1671,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1687,234 +1712,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>278500</v>
+      </c>
+      <c r="E17" s="3">
         <v>281200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>265800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>249400</v>
       </c>
-      <c r="G17" s="3">
-        <v>282000</v>
-      </c>
       <c r="H17" s="3">
+        <v>282200</v>
+      </c>
+      <c r="I17" s="3">
         <v>302500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>277500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>260200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>292000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>270000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>260200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>262100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>298100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>273500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>282100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>285500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>293900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>272500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>270900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>243300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>254400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>286400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>170800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>235100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>256500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>252500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>238200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>233200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>253200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>253400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>240100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>243100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>269600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>468800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>240200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>235700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E18" s="3">
         <v>25200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13500</v>
       </c>
-      <c r="G18" s="3">
-        <v>24900</v>
-      </c>
       <c r="H18" s="3">
+        <v>24700</v>
+      </c>
+      <c r="I18" s="3">
         <v>30200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>62400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>57600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>19700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>13200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1954,8 +1986,9 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1989,20 +2022,20 @@
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
-        <v>400</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
         <v>400</v>
       </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -2023,19 +2056,19 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>300</v>
       </c>
       <c r="AD20" s="3">
         <v>300</v>
@@ -2044,11 +2077,11 @@
         <v>300</v>
       </c>
       <c r="AF20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -2067,121 +2100,127 @@
       <c r="AM20" s="3">
         <v>0</v>
       </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E21" s="3">
         <v>33700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19100</v>
       </c>
-      <c r="G21" s="3">
-        <v>32500</v>
-      </c>
       <c r="H21" s="3">
+        <v>32300</v>
+      </c>
+      <c r="I21" s="3">
         <v>37900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>30200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>35700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>50200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>44700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>33000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>67200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>64300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>61900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>14600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>18400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>19900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>20200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>21600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>20600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>23000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>31600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>19100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2192,10 +2231,10 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
         <v>-100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -2252,17 +2291,17 @@
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
@@ -2279,248 +2318,257 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>200</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
       <c r="AL22" s="3">
         <v>0</v>
       </c>
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E23" s="3">
         <v>25900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>30600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>43900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>27800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>62300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>59600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>57500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>14300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>18300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>15700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>19500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>13200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>7300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2632,234 +2680,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E26" s="3">
         <v>19200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>28900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>46800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>44200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>43200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>14700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>13700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>13900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>11700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>13000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>12100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>8200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E27" s="3">
         <v>19200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>46800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>44200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>43200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>13800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>12000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>8100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2971,8 +3028,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3042,8 +3102,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3054,24 +3114,24 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3084,8 +3144,11 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3197,8 +3260,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3310,8 +3376,11 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3345,20 +3414,20 @@
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
-        <v>-400</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
         <v>-400</v>
       </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -3379,19 +3448,19 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-300</v>
       </c>
       <c r="AD32" s="3">
         <v>-300</v>
@@ -3400,11 +3469,11 @@
         <v>-300</v>
       </c>
       <c r="AF32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3423,121 +3492,127 @@
       <c r="AM32" s="3">
         <v>0</v>
       </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E33" s="3">
         <v>19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>46800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>44200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>43200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>13700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>13800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>12000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>8100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3649,239 +3724,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E35" s="3">
         <v>19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>46800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>44200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>43200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>13700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>13800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>12000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>8100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45962</v>
+      </c>
+      <c r="E38" s="2">
         <v>45871</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45780</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45689</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45598</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45507</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45416</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45325</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45227</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45136</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45045</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44954</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44863</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44772</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44590</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44499</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44317</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44226</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44044</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43953</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43862</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43771</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43680</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43589</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43498</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43407</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43316</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43225</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43134</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43036</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42945</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42854</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42763</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3921,8 +4005,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3962,178 +4047,182 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E41" s="3">
         <v>78700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>108700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>56900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>99000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>32600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>51600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>117400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>173400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>146500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>174600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>106500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>46700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>76900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>61900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>33700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>37500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>67000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>39700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>38400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>35300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>48300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>21100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>18500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>25300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>62900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E42" s="3">
         <v>13200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10400</v>
-      </c>
-      <c r="P42" s="3">
-        <v>11000</v>
       </c>
       <c r="Q42" s="3">
         <v>11000</v>
       </c>
       <c r="R42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="S42" s="3">
         <v>15000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>17800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>17400</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4149,8 +4238,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -4188,460 +4277,475 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E43" s="3">
         <v>8500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>3100</v>
       </c>
       <c r="N43" s="3">
         <v>3100</v>
       </c>
       <c r="O43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>435300</v>
+      </c>
+      <c r="E44" s="3">
         <v>449000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>428400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>385600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>406600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>425500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>411600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>346400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>368300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>409300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>389500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>390400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>392300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>385500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>345000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>285200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>282000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>308100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>268600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>233300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>274300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>298900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>304000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>259500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>298000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>336900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>289400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>257500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>300500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>336900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>295900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>260500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>302900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>357500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>309600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>279600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E45" s="3">
         <v>24700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5500</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>10900</v>
       </c>
       <c r="AB45" s="3">
         <v>10900</v>
       </c>
       <c r="AC45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AD45" s="3">
         <v>9800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>13200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>6900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>6700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E46" s="3">
         <v>574100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>548600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>536100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>527000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>537100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>505000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>481300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>462000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>485400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>453600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>469700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>464400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>476900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>471200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>442000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>495700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>493100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>462600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>355300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>340200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>396000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>337600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>329600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>345000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>387700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>322700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>337300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>354300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>391300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>347600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>320600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>338200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>385800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>343500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>351800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4675,8 +4779,8 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4753,121 +4857,127 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>528700</v>
+      </c>
+      <c r="E48" s="3">
         <v>520300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>520200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>516400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>525200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>508600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>518100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>502500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>502800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>498800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>463200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>460000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>442200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>379300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>332300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>309500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>273500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>274300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>269600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>268000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>265100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>275600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>275300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>282800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>291300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>294400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>297000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>70600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>74500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>77300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>81600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>86300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>93000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>96000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>97300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>96200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4878,22 +4988,22 @@
         <v>59000</v>
       </c>
       <c r="F49" s="3">
+        <v>59000</v>
+      </c>
+      <c r="G49" s="3">
         <v>70200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>59000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>56400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>56200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>57100</v>
-      </c>
-      <c r="K49" s="3">
-        <v>44600</v>
       </c>
       <c r="L49" s="3">
         <v>44600</v>
@@ -4905,20 +5015,20 @@
         <v>44600</v>
       </c>
       <c r="O49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="P49" s="3">
         <v>44100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>43400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>44300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>44000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4934,8 +5044,8 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4979,8 +5089,11 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5092,8 +5205,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5205,121 +5321,127 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E52" s="3">
         <v>11900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>19500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>15900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>10500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5431,121 +5553,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1172500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1165300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1140200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1124100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1124400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1115000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1092600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1042000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1023500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1043200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>976600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>989800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>966300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>914500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>861700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>812300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>786500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>784100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>750100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>642700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>623300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>689500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>629600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>628400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>647700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>693400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>628600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>418000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>438000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>477300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>437900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>415600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>442700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>492800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>451400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>458500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5585,8 +5713,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5626,157 +5755,161 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E57" s="3">
         <v>68700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>73900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>71200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>42900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>77400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>55900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>78900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>88300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>113800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>116800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>69100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>65600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>96500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>102400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>57700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>50900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>129600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>90000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>60700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>66100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>108400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>56500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>48700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>56300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>90900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>62600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>41700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>59400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>93800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>70600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>67800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E58" s="3">
         <v>57900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>58400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>53000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>58400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>55900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>56000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>53000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>57100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>57300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>58100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5852,270 +5985,279 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5900</v>
       </c>
-      <c r="G59" s="3">
-        <v>4600</v>
-      </c>
       <c r="H59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I59" s="3">
         <v>5500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>4300</v>
       </c>
       <c r="M59" s="3">
         <v>4300</v>
       </c>
       <c r="N59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O59" s="3">
         <v>78400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>75400</v>
       </c>
       <c r="P59" s="3">
         <v>75400</v>
       </c>
       <c r="Q59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="R59" s="3">
         <v>82500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>96200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>97900</v>
       </c>
       <c r="U59" s="3">
         <v>97900</v>
       </c>
       <c r="V59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="W59" s="3">
         <v>73200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>74300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>66200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>61600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>61800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>64500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>67000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>64700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>28100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>25700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>24200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>20400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>21900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>18500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E60" s="3">
         <v>156500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>149600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>130400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>135800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>160000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>149200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>127900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>121400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>154800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>135200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>157300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>163800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>189200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>199400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>153700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>161800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>194400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>200300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>130900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>125200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>195900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>151600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>122500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>130600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>175400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>121200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>70800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>84400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>116600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>86800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>56800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>81300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>114200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>92400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>86300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E61" s="3">
         <v>303700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>307000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>315000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>317700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>304600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>313300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>301400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>305300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>307300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>279200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6180,132 +6322,138 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>26700</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>306900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>297000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>241600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>206700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>206000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>192100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>199800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>199500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>201700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>194900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>204700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>198500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>208500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>216300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>214400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>215900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>42800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>44900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>47000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>49600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>51500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>51800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>51700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>52300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>53300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6417,8 +6565,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6530,8 +6681,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6643,121 +6797,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>489400</v>
+      </c>
+      <c r="E66" s="3">
         <v>494600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>486600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>475100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>488800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>496500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>494800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>458600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>453600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>487700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>438900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>464200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>460800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>430900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>406000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>359700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>354000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>394100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>399800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>332600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>320100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>400500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>350100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>331000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>347000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>389800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>337100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>113600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>129300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>163500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>136400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>108300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>133100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>192600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>144700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>139600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6797,8 +6957,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6910,8 +7071,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7023,8 +7187,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7136,8 +7303,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7249,121 +7419,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>803900</v>
+      </c>
+      <c r="E72" s="3">
         <v>793500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>778500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>773400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>762500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>747000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>728200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>714600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>702400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>683900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>667200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>653500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>634300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>604200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>577800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>553500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>534900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>490100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>447900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>406700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>400500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>387100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>378400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>395800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>393500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>381000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>370500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>360400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>360300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>349500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>339100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>326700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>331900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>322500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>319900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>312600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7475,8 +7651,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7588,8 +7767,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7701,121 +7883,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>683200</v>
+      </c>
+      <c r="E76" s="3">
         <v>670700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>653600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>649000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>635700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>618500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>597800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>583400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>569900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>555500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>537700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>525600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>505600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>483600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>455700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>452500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>432500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>389900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>350300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>310200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>303200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>289000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>279500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>297400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>300700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>303600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>291500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>304400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>308800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>313800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>301500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>307300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>309600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>300200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>306600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>318900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7927,239 +8115,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45962</v>
+      </c>
+      <c r="E80" s="2">
         <v>45871</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45780</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45689</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45598</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45507</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45416</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45325</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45227</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45136</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45045</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44954</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44863</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44772</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44590</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44499</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44317</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44226</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44044</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43953</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43862</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43771</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43680</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43589</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43498</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43407</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43316</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43225</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43134</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43036</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42945</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42854</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42763</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E81" s="3">
         <v>19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>46800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>44200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>43200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>13700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>13800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>12000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>8100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8199,121 +8396,125 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E83" s="3">
         <v>7700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3800</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>4300</v>
       </c>
       <c r="AA83" s="3">
         <v>4300</v>
       </c>
       <c r="AB83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AC83" s="3">
         <v>4100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4300</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>5300</v>
       </c>
       <c r="AE83" s="3">
         <v>5300</v>
       </c>
       <c r="AF83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="AG83" s="3">
         <v>5600</v>
       </c>
       <c r="AH83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AI83" s="3">
         <v>5900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>12000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8425,8 +8626,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8538,8 +8742,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8651,8 +8858,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8764,8 +8974,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8877,121 +9090,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E89" s="3">
         <v>13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>44600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>40600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>76500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>63200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-26000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>69100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-42900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>38900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>18000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>19300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>23600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>31400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>35500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>42300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9031,121 +9250,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-2400</v>
       </c>
       <c r="AE91" s="3">
         <v>-2400</v>
       </c>
       <c r="AF91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9257,8 +9480,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9370,121 +9596,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-81400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-25500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9524,8 +9756,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9533,10 +9766,10 @@
         <v>4100</v>
       </c>
       <c r="E96" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F96" s="3">
         <v>4400</v>
-      </c>
-      <c r="F96" s="3">
-        <v>3700</v>
       </c>
       <c r="G96" s="3">
         <v>3700</v>
@@ -9548,31 +9781,31 @@
         <v>3700</v>
       </c>
       <c r="J96" s="3">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="K96" s="3">
         <v>3300</v>
       </c>
       <c r="L96" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M96" s="3">
         <v>2700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-2500</v>
       </c>
       <c r="P96" s="3">
         <v>-2500</v>
       </c>
       <c r="Q96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-2000</v>
       </c>
       <c r="S96" s="3">
         <v>-2000</v>
@@ -9581,10 +9814,10 @@
         <v>-2000</v>
       </c>
       <c r="U96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-1300</v>
       </c>
       <c r="W96" s="3">
         <v>-1300</v>
@@ -9596,7 +9829,7 @@
         <v>-1300</v>
       </c>
       <c r="Z96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="AA96" s="3">
         <v>-1200</v>
@@ -9605,10 +9838,10 @@
         <v>-1200</v>
       </c>
       <c r="AC96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AE96" s="3">
         <v>-1200</v>
@@ -9626,10 +9859,10 @@
         <v>-1200</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AL96" s="3">
         <v>-1200</v>
@@ -9637,8 +9870,11 @@
       <c r="AM96" s="3">
         <v>-1200</v>
       </c>
+      <c r="AN96" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9750,8 +9986,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9863,8 +10102,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9976,8 +10218,11 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9985,112 +10230,115 @@
         <v>-4100</v>
       </c>
       <c r="E100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-6500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-3600</v>
       </c>
       <c r="H100" s="3">
         <v>-3600</v>
       </c>
       <c r="I100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J100" s="3">
         <v>-4400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-1200</v>
       </c>
       <c r="W100" s="3">
         <v>-1200</v>
       </c>
       <c r="X100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-26900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-21200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10124,8 +10372,8 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -10202,117 +10450,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>31400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-42100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-55900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>26900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-28100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>68100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>59800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-30100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>63800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-48800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>28200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>15800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-45400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>27300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>27200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>29400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-8000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,520 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45962</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45871</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45780</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45689</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45598</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45507</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45416</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45325</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45227</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45136</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45045</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44954</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44863</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44590</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44499</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44317</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44226</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44044</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43953</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43862</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43771</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43680</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43589</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43498</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43407</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43316</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43225</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43134</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43036</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42945</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42854</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42763</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>254100</v>
+      </c>
+      <c r="E8" s="3">
         <v>297200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>306400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>277700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>262900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>306900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>332700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>280200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>319900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>294600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>281200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>290800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>341700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>312300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>317500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>313400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>356300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>332200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>328500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>253900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>274600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>300800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>147500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>239900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>274600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>268200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>253800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>234700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>269200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>268400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>257400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>243200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>287500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>488500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>253400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>234200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>274500</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>165300</v>
+      </c>
+      <c r="E9" s="3">
         <v>185300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>187600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>181900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>171300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>196500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>212800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>193600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>180500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>202200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>189200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>182700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>179500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>210800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>199100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>204700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>196600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>212300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>196500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>198300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>175700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>186800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>218200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>116000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>170000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>189900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>186100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>178700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>168000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>188000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>184600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>180100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>173000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>201800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>348100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>181200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>169800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>192500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E10" s="3">
         <v>111800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>118800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>95800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>91700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>110400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>119900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>106800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>117700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>105500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>98500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>111300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>130900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>113200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>112800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>116900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>144000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>135700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>130200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>78200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>87800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>82600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>31500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>69900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>84700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>82100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>75100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>66700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>81200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>83800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>77300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>70200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>85700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>140400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>72200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>64400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1223,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1326,8 +1340,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1442,8 +1459,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1456,21 +1476,21 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>-500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>100</v>
       </c>
       <c r="I14" s="3">
         <v>100</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1480,11 +1500,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1492,44 +1512,44 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3100</v>
-      </c>
-      <c r="X14" s="3">
-        <v>200</v>
       </c>
       <c r="Y14" s="3">
         <v>200</v>
       </c>
       <c r="Z14" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA14" s="3">
         <v>2300</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>600</v>
       </c>
       <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1540,8 +1560,8 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1558,47 +1578,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E15" s="3">
         <v>8600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6700</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1674,8 +1697,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,240 +1739,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>243100</v>
+      </c>
+      <c r="E17" s="3">
         <v>278500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>281200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>265800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>249400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>282200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>302500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>277500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>292000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>270000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>260200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>262100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>298100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>273500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>282100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>285500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>293900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>272500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>270900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>243300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>254400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>286400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>170800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>235100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>256500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>252500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>238200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>233200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>253200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>253400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>240100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>243100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>269600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>468800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>240200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>235700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>259100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E18" s="3">
         <v>18600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>38800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>35400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>27900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>62400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>59700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>57600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>17900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>19700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>13200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1987,8 +2020,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2004,8 +2038,8 @@
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
+      <c r="H20" s="3">
+        <v>-3000</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
@@ -2025,20 +2059,20 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>400</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>400</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -2059,19 +2093,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
       <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>300</v>
       </c>
       <c r="AE20" s="3">
         <v>300</v>
@@ -2080,11 +2114,11 @@
         <v>300</v>
       </c>
       <c r="AG20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
@@ -2103,124 +2137,130 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E21" s="3">
         <v>27200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>22100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>32300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>30200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>24600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>35300</v>
+      </c>
+      <c r="N21" s="3">
+        <v>31800</v>
+      </c>
+      <c r="O21" s="3">
+        <v>27600</v>
+      </c>
+      <c r="P21" s="3">
+        <v>35700</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>50200</v>
+      </c>
+      <c r="R21" s="3">
+        <v>44700</v>
+      </c>
+      <c r="S21" s="3">
+        <v>40100</v>
+      </c>
+      <c r="T21" s="3">
+        <v>33000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>67200</v>
+      </c>
+      <c r="V21" s="3">
+        <v>64300</v>
+      </c>
+      <c r="W21" s="3">
+        <v>61900</v>
+      </c>
+      <c r="X21" s="3">
+        <v>14600</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>24300</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>18400</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>22600</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>19900</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>20200</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>21600</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>20600</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AK21" s="3">
+        <v>23900</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>31600</v>
+      </c>
+      <c r="AM21" s="3">
         <v>19100</v>
       </c>
-      <c r="H21" s="3">
-        <v>32300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>37900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>30200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>24600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>35300</v>
-      </c>
-      <c r="M21" s="3">
-        <v>31800</v>
-      </c>
-      <c r="N21" s="3">
-        <v>27600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>35700</v>
-      </c>
-      <c r="P21" s="3">
-        <v>50200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>44700</v>
-      </c>
-      <c r="R21" s="3">
-        <v>40100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>33000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>67200</v>
-      </c>
-      <c r="U21" s="3">
-        <v>64300</v>
-      </c>
-      <c r="V21" s="3">
-        <v>61900</v>
-      </c>
-      <c r="W21" s="3">
-        <v>14600</v>
-      </c>
-      <c r="X21" s="3">
-        <v>24300</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>18400</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-19300</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>22600</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>19900</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>20200</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>7100</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>21600</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>20600</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>23000</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AJ21" s="3">
-        <v>23900</v>
-      </c>
-      <c r="AK21" s="3">
-        <v>31600</v>
-      </c>
-      <c r="AL21" s="3">
-        <v>19100</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2234,10 +2274,10 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3">
         <v>-100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -2294,17 +2334,17 @@
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
@@ -2321,254 +2361,263 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>200</v>
       </c>
-      <c r="AL22" s="3">
-        <v>0</v>
-      </c>
       <c r="AM22" s="3">
         <v>0</v>
       </c>
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E23" s="3">
         <v>19600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>30600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>43900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>62300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>59600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>57500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>15900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>17800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>19500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>13200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>7100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>7300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>5000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2683,240 +2732,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E26" s="3">
         <v>14600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>28900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>46800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>44200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>43200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>13700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>11800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>13900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>12000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>11700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>13000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>10700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>12100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>8200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E27" s="3">
         <v>14600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>28900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>26900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>46800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>44200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>43200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>13700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>13800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>11600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>10500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>12000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>8100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3031,8 +3089,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3105,8 +3166,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3117,24 +3178,24 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>100</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3147,8 +3208,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3327,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,8 +3446,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3396,8 +3466,8 @@
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
+      <c r="H32" s="3">
+        <v>3000</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
@@ -3417,20 +3487,20 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>-400</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>-400</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -3451,19 +3521,19 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-300</v>
       </c>
       <c r="AE32" s="3">
         <v>-300</v>
@@ -3472,11 +3542,11 @@
         <v>-300</v>
       </c>
       <c r="AG32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
@@ -3495,124 +3565,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E33" s="3">
         <v>14600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>28900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>20600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>46800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>44200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>43200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>13700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>13800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>11700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>10500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>12000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>8100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,245 +3803,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E35" s="3">
         <v>14600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>28900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>20600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>46800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>44200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>43200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>13700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>13800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>11700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>10500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>12000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>8100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45962</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45871</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45780</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45689</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45598</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45507</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45416</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45325</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45227</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45136</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45045</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44954</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44863</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44772</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44590</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44499</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44317</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44226</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44044</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43953</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43862</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43771</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43680</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43589</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43498</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43407</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43316</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43225</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43134</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43036</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42945</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42854</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42763</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4091,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,184 +4134,188 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E41" s="3">
         <v>94400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>108700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>56900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>99000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>51400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>117400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>173400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>146500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>174600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>106500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>46700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>76900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>61900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>33700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>37500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>21600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>67000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>39700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>38400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>35300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>21100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>18500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>25300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>62900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E42" s="3">
         <v>13300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10400</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>11000</v>
       </c>
       <c r="R42" s="3">
         <v>11000</v>
       </c>
       <c r="S42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="T42" s="3">
         <v>15000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>17800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>17400</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4241,8 +4331,8 @@
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -4280,472 +4370,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>3100</v>
       </c>
       <c r="O43" s="3">
         <v>3100</v>
       </c>
       <c r="P43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>7800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>439600</v>
+      </c>
+      <c r="E44" s="3">
         <v>435300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>449000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>428400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>385600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>406600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>425500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>411600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>346400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>368300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>409300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>389500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>390400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>392300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>385500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>345000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>285200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>282000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>308100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>268600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>233300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>274300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>298900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>304000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>259500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>298000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>336900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>289400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>257500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>300500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>336900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>295900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>260500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>302900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>357500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>309600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>279600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E45" s="3">
         <v>23000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5500</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>10900</v>
       </c>
       <c r="AC45" s="3">
         <v>10900</v>
       </c>
       <c r="AD45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AE45" s="3">
         <v>9800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>11800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>13200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>6700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>596100</v>
+      </c>
+      <c r="E46" s="3">
         <v>573000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>574100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>548600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>536100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>527000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>537100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>505000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>481300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>462000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>485400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>453600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>469700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>464400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>476900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>471200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>442000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>495700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>493100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>462600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>355300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>340200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>396000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>337600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>329600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>345000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>387700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>322700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>337300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>354300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>391300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>347600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>320600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>338200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>385800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>343500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>351800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>357600</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4782,8 +4887,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4860,129 +4965,135 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>535200</v>
+      </c>
+      <c r="E48" s="3">
         <v>528700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>520300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>520200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>516400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>525200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>508600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>518100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>502500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>502800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>498800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>463200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>460000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>442200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>379300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>332300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>309500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>273500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>274300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>269600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>268000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>265100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>275600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>275300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>282800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>291300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>294400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>297000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>70600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>74500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>77300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>81600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>86300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>93000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>96000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>97300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>96200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>59000</v>
+        <v>68400</v>
       </c>
       <c r="E49" s="3">
         <v>59000</v>
@@ -4991,22 +5102,22 @@
         <v>59000</v>
       </c>
       <c r="G49" s="3">
+        <v>59000</v>
+      </c>
+      <c r="H49" s="3">
         <v>70200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>56400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>56200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>57100</v>
-      </c>
-      <c r="L49" s="3">
-        <v>44600</v>
       </c>
       <c r="M49" s="3">
         <v>44600</v>
@@ -5018,20 +5129,20 @@
         <v>44600</v>
       </c>
       <c r="P49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="Q49" s="3">
         <v>44100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>43400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>44300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>44000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5047,8 +5158,8 @@
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -5092,8 +5203,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5322,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,124 +5441,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>19500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>15900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>11400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>10600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,124 +5679,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1201700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1172500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1165300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1140200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1124100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1124400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1115000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1092600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1042000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1023500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1043200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>976600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>989800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>966300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>914500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>861700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>812300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>786500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>784100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>750100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>642700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>623300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>689500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>629600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>628400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>647700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>693400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>628600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>418000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>438000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>477300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>437900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>415600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>442700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>492800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>451400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>458500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>469700</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5843,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,163 +5886,167 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E57" s="3">
         <v>65900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>68700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>66600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>73900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>71200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>58300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>42900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>77400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>78900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>88300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>113800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>116800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>65600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>96500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>102400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>57700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>50900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>129600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>90000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>60700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>66100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>108400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>56500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>56300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>90900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>62600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>41700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>59400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>93800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>70600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>67800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E58" s="3">
         <v>51900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>57900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>58400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>58400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>55900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>56000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>57100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>57300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>58100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5988,279 +6122,288 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>4300</v>
       </c>
       <c r="N59" s="3">
         <v>4300</v>
       </c>
       <c r="O59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P59" s="3">
         <v>78400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>75400</v>
       </c>
       <c r="Q59" s="3">
         <v>75400</v>
       </c>
       <c r="R59" s="3">
+        <v>75400</v>
+      </c>
+      <c r="S59" s="3">
         <v>82500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>84600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>96200</v>
-      </c>
-      <c r="U59" s="3">
-        <v>97900</v>
       </c>
       <c r="V59" s="3">
         <v>97900</v>
       </c>
       <c r="W59" s="3">
+        <v>97900</v>
+      </c>
+      <c r="X59" s="3">
         <v>73200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>74300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>66200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>61600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>61800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>64500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>67000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>64700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>22100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>28100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>25700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>24200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>21900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>20400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>21900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>18500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>158400</v>
+      </c>
+      <c r="E60" s="3">
         <v>141300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>156500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>149600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>130400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>135800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>160000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>149200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>127900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>121400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>154800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>135200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>157300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>163800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>189200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>199400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>153700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>161800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>194400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>200300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>130900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>125200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>195900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>151600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>122500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>130600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>175400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>121200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>70800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>84400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>116600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>86800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>56800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>81300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>114200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>92400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>86300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>313400</v>
+      </c>
+      <c r="E61" s="3">
         <v>310900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>303700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>307000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>315000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>317700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>304600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>313300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>301400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>305300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>307300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>279200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6325,135 +6468,141 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>26700</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E62" s="3">
         <v>12000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>306900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>297000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>241600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>206700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>206000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>192100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>199800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>199500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>201700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>194900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>204700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>198500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>208500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>216300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>214400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>215900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>42800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>44900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>47000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>49600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>51500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>51800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>51700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>52300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>53300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6717,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,8 +6836,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,124 +6955,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>512100</v>
+      </c>
+      <c r="E66" s="3">
         <v>489400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>494600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>486600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>475100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>488800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>496500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>494800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>458600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>453600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>487700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>438900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>464200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>460800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>430900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>406000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>359700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>354000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>394100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>399800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>332600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>320100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>350100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>331000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>347000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>389800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>337100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>113600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>129300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>163500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>136400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>108300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>133100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>192600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>144700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>139600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>141600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7119,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7236,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7355,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7474,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,124 +7593,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>808800</v>
+      </c>
+      <c r="E72" s="3">
         <v>803900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>793500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>778500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>773400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>762500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>747000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>728200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>714600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>702400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>683900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>667200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>653500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>634300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>604200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>577800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>553500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>534900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>490100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>447900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>406700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>400500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>387100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>378400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>395800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>393500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>381000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>370500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>360400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>360300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>349500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>339100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>326700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>331900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>322500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>319900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>312600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +7831,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +7950,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,124 +8069,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>689700</v>
+      </c>
+      <c r="E76" s="3">
         <v>683200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>670700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>653600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>649000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>635700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>618500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>597800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>583400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>569900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>555500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>537700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>525600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>505600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>483600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>455700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>452500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>432500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>389900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>350300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>310200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>303200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>289000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>279500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>297400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>300700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>303600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>291500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>304400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>308800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>313800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>301500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>307300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>309600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>300200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>306600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>318900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,245 +8307,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45962</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45871</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45780</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45689</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45598</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45507</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45416</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45325</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45227</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45136</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45045</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44954</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44863</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44772</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44590</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44499</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44317</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44226</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44044</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43953</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43862</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43771</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43680</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43589</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43498</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43407</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43316</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43225</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43134</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43036</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42945</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42854</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42763</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E81" s="3">
         <v>14600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>28900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>20600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>46800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>44200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>43200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>13700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>13800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>11700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>10500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>12000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>8100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,124 +8595,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E83" s="3">
         <v>7600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3800</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>4300</v>
       </c>
       <c r="AB83" s="3">
         <v>4300</v>
       </c>
       <c r="AC83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AD83" s="3">
         <v>4100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4300</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>5300</v>
       </c>
       <c r="AF83" s="3">
         <v>5300</v>
       </c>
       <c r="AG83" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="AH83" s="3">
         <v>5600</v>
       </c>
       <c r="AI83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>6000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>12000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>5800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>6000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +8831,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +8950,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9069,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9188,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,124 +9307,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E89" s="3">
         <v>33600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>44600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>53400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>76500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>63200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>69100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-42900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>38900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>18000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>19300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>36400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>23600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>31400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>35500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-26500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-9700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>42300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,124 +9471,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-23300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-2400</v>
       </c>
       <c r="AF91" s="3">
         <v>-2400</v>
       </c>
       <c r="AG91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9707,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,124 +9826,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-81400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-25500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,8 +9990,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9769,10 +10003,10 @@
         <v>4100</v>
       </c>
       <c r="F96" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G96" s="3">
         <v>4400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>3700</v>
       </c>
       <c r="H96" s="3">
         <v>3700</v>
@@ -9784,31 +10018,31 @@
         <v>3700</v>
       </c>
       <c r="K96" s="3">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="L96" s="3">
         <v>3300</v>
       </c>
       <c r="M96" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N96" s="3">
         <v>2700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-2500</v>
       </c>
       <c r="Q96" s="3">
         <v>-2500</v>
       </c>
       <c r="R96" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="S96" s="3">
         <v>-2600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-2000</v>
       </c>
       <c r="T96" s="3">
         <v>-2000</v>
@@ -9817,10 +10051,10 @@
         <v>-2000</v>
       </c>
       <c r="V96" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-2100</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-1300</v>
       </c>
       <c r="X96" s="3">
         <v>-1300</v>
@@ -9832,7 +10066,7 @@
         <v>-1300</v>
       </c>
       <c r="AA96" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="AB96" s="3">
         <v>-1200</v>
@@ -9841,10 +10075,10 @@
         <v>-1200</v>
       </c>
       <c r="AD96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AF96" s="3">
         <v>-1200</v>
@@ -9862,10 +10096,10 @@
         <v>-1200</v>
       </c>
       <c r="AK96" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-1200</v>
       </c>
       <c r="AM96" s="3">
         <v>-1200</v>
@@ -9873,8 +10107,11 @@
       <c r="AN96" s="3">
         <v>-1200</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10226,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10345,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,124 +10464,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="E100" s="3">
         <v>-4100</v>
       </c>
       <c r="F100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="G100" s="3">
         <v>-6500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-3600</v>
       </c>
       <c r="I100" s="3">
         <v>-3600</v>
       </c>
       <c r="J100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-1200</v>
       </c>
       <c r="X100" s="3">
         <v>-1200</v>
       </c>
       <c r="Y100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-26900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-21200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-29000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-20500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10375,8 +10624,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10453,120 +10702,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E102" s="3">
         <v>15700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>31400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-34600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-31300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-55900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>68100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>59800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-30100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>63800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-48800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>28200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>15800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-45400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>27300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>27200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-44400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-37700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>29400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-8000</v>
       </c>
     </row>
